--- a/Assets/Documents/全局配置表.xlsx
+++ b/Assets/Documents/全局配置表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Projects\Unity\MagicSoup\Assets\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\何睿豪\Documents\GitHub\MagicSoup\Assets\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B13A94-E8BF-4323-BE59-39B622CD224F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC6E48B-84F7-4FCB-AD04-CC06781FADAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="素材库" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -46,10 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>胡萝卜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>生命值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +216,10 @@
   </si>
   <si>
     <t>注释：同小怪池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混合肉饼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -560,18 +557,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="18.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="2" customWidth="1"/>
-    <col min="6" max="7" width="20.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="20.21875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="57" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,36 +576,36 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2">
         <v>5</v>
       </c>
       <c r="D2" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -617,12 +614,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
@@ -637,19 +634,165 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E5" s="2">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E7" s="2">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" s="2">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E9" s="2">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E10" s="2">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="2">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E12" s="2">
+        <v>21</v>
+      </c>
+      <c r="F12" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="2">
+        <v>23</v>
+      </c>
+      <c r="F13" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E14" s="2">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E15" s="2">
+        <v>27</v>
+      </c>
+      <c r="F15" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E16" s="2">
+        <v>29</v>
+      </c>
+      <c r="F16" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="2">
+        <v>31</v>
+      </c>
+      <c r="F17" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="2">
+        <v>33</v>
+      </c>
+      <c r="F18" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E19" s="2">
+        <v>35</v>
+      </c>
+      <c r="F19" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E20" s="2">
+        <v>37</v>
+      </c>
+      <c r="F20" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E21" s="2">
+        <v>39</v>
+      </c>
+      <c r="F21" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E22" s="2">
+        <v>41</v>
+      </c>
+      <c r="F22" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -662,97 +805,97 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919218B-E131-4143-AB50-79A72E51C644}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="29.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" style="2" customWidth="1"/>
     <col min="5" max="5" width="16" style="2" customWidth="1"/>
     <col min="6" max="8" width="9" style="2"/>
-    <col min="9" max="9" width="20.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20.77734375" style="2" customWidth="1"/>
     <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.21875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="138" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -764,9 +907,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1074A89F-2652-443D-BB3C-BB014D324722}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -774,10 +917,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -791,42 +934,42 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3568C53C-0336-4118-8C36-0FB9EB26128F}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="45.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.44140625" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -840,50 +983,50 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F438E8A-FCA7-40DE-9EE5-7F73BB8BE90C}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -895,20 +1038,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B514FEB-CB79-4116-8D56-FF07CAAEE429}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -922,50 +1065,50 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D2A9B2-6CD1-4D46-9EC7-7CDE15559BEB}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="9" style="3"/>
     <col min="6" max="6" width="15" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="69" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -980,32 +1123,32 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5139357-4865-410A-B8A0-193B24F73826}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" t="s">
-        <v>39</v>
-      </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1019,32 +1162,32 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE6E2BC-2530-45EC-B0CD-4849549B7D87}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" t="s">
-        <v>39</v>
-      </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>

--- a/Assets/Documents/全局配置表.xlsx
+++ b/Assets/Documents/全局配置表.xlsx
@@ -1,225 +1,1553 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\何睿豪\Documents\GitHub\MagicSoup\Assets\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\何睿豪\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC6E48B-84F7-4FCB-AD04-CC06781FADAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A8946C-2FCF-4FF7-9EDE-EA3272574CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="素材库" sheetId="1" r:id="rId1"/>
-    <sheet name="意图库" sheetId="9" r:id="rId2"/>
-    <sheet name="药水库" sheetId="13" r:id="rId3"/>
-    <sheet name="玩家素材池" sheetId="2" r:id="rId4"/>
-    <sheet name="遗物库" sheetId="4" r:id="rId5"/>
-    <sheet name="玩家遗物池" sheetId="5" r:id="rId6"/>
-    <sheet name="小怪池" sheetId="3" r:id="rId7"/>
-    <sheet name="精英池" sheetId="7" r:id="rId8"/>
-    <sheet name="boss池" sheetId="10" r:id="rId9"/>
+    <sheet name="意图库" sheetId="2" r:id="rId2"/>
+    <sheet name="药水库" sheetId="3" r:id="rId3"/>
+    <sheet name="玩家素材池" sheetId="4" r:id="rId4"/>
+    <sheet name="遗物库" sheetId="5" r:id="rId5"/>
+    <sheet name="玩家遗物池" sheetId="6" r:id="rId6"/>
+    <sheet name="小怪池" sheetId="7" r:id="rId7"/>
+    <sheet name="精英池" sheetId="8" r:id="rId8"/>
+    <sheet name="boss池" sheetId="9" r:id="rId9"/>
+    <sheet name="合成表" sheetId="10" r:id="rId10"/>
+    <sheet name="角色" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="506">
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>升级后生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图列表索引</t>
+  </si>
+  <si>
+    <t>升级后意图列表索引</t>
+  </si>
+  <si>
+    <t>注释：这个表描述的是游戏中所有的素材，包括玩家卡牌素材和怪物卡牌素材</t>
+  </si>
+  <si>
+    <t>注释：列表索引会指向意图库里面对应的意图列表</t>
+  </si>
+  <si>
+    <t>混合肉饼</t>
+  </si>
+  <si>
+    <t>混合肉块</t>
+  </si>
+  <si>
+    <t>混合碎肉</t>
+  </si>
+  <si>
+    <t>混合精肉饼</t>
+  </si>
+  <si>
+    <t>混合精肉块</t>
+  </si>
+  <si>
+    <t>混合精碎肉</t>
+  </si>
+  <si>
+    <t>特级混合精肉饼</t>
+  </si>
+  <si>
+    <t>特级混合精肉块</t>
+  </si>
+  <si>
+    <t>特级混合精碎肉</t>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+  </si>
+  <si>
+    <t>土鸡蛋</t>
+  </si>
+  <si>
+    <t>特级土鸡蛋</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>山泉水</t>
+  </si>
+  <si>
+    <t>特级山泉水</t>
+  </si>
+  <si>
+    <t>姜</t>
+  </si>
+  <si>
+    <t>香菇</t>
+  </si>
+  <si>
+    <t>干香菇</t>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
+    <t>糊的肉</t>
+  </si>
+  <si>
+    <t>焦炭</t>
+  </si>
+  <si>
+    <t>虾米</t>
+  </si>
+  <si>
+    <t>精品猪后腿肉</t>
+  </si>
+  <si>
+    <t>咸水</t>
+  </si>
+  <si>
+    <t>特级精品猪油</t>
+  </si>
+  <si>
+    <t>海水</t>
+  </si>
+  <si>
+    <t>海藻气泡</t>
+  </si>
+  <si>
+    <t>海藻团块</t>
+  </si>
+  <si>
+    <t>咸汤</t>
+  </si>
+  <si>
+    <t>Less4 Attack2</t>
+  </si>
+  <si>
+    <t>Greater8 Attack1*2</t>
+  </si>
+  <si>
+    <t>注释：意图用空格分成两部分。第一部分是触发条件。None代表无条件。Equal代表当前时钟值等于某个值才满足。Notequal代表当前时钟值不等于某个值才满足。Less和Greater分别代表当前时钟值小于和大于某个值才满足</t>
+  </si>
+  <si>
+    <t>第二部分是指向的动作。目前有三种动作，Attack代表攻击第一个敌方卡牌，Heal和Defence分别代表治疗自身和给自己加护甲。</t>
+  </si>
+  <si>
+    <t>目前的意图条件和行动类型只开发了这些。如果要定义新的意图条件和行动类型，需要说清楚</t>
+  </si>
+  <si>
+    <t>Equal6 Attack2</t>
+  </si>
+  <si>
+    <t>Greater5 Attack2</t>
+  </si>
+  <si>
+    <t>Equal1 Attack1</t>
+  </si>
+  <si>
+    <t>Equal3 Attack1</t>
+  </si>
+  <si>
+    <t>Equal5 Attack1</t>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack0 | Equal12 Attack0</t>
+  </si>
+  <si>
+    <t>Less6 Attack2</t>
+  </si>
+  <si>
+    <t>Greater6 Attack1*2</t>
+  </si>
+  <si>
+    <t>Equal6 Attack4</t>
+  </si>
+  <si>
+    <t>Greater3 Attack2</t>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack1 | Equal12 Attack1</t>
+  </si>
+  <si>
+    <t>Equal6 Attack1</t>
+  </si>
+  <si>
+    <t>Equal12 Attack1</t>
+  </si>
+  <si>
+    <t>Less7 Attack4</t>
+  </si>
+  <si>
+    <t>Greater5 Attack1*3</t>
+  </si>
+  <si>
+    <t>Equal6 Attack8</t>
+  </si>
+  <si>
+    <t>Greater0 Attack2</t>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal1 Attack1 | Equal6 Attack1 | Equal12 Attack1</t>
+  </si>
+  <si>
+    <t>None Heal2</t>
+  </si>
+  <si>
+    <t>None Attack2</t>
+  </si>
+  <si>
+    <t>None Defence2</t>
+  </si>
+  <si>
+    <t>Less13 Defence2</t>
+  </si>
+  <si>
+    <t>None Attack3</t>
+  </si>
+  <si>
+    <t>Less13 Defence3</t>
+  </si>
+  <si>
+    <t>None Heal5</t>
+  </si>
+  <si>
+    <t>None Heal1</t>
+  </si>
+  <si>
+    <t>None Heal6</t>
+  </si>
+  <si>
+    <t>None Heal3</t>
+  </si>
+  <si>
+    <t>None Heal10</t>
+  </si>
+  <si>
+    <t>Less12 Defence1</t>
+  </si>
+  <si>
+    <t>None Attack0</t>
+  </si>
+  <si>
+    <t>None Heal-2</t>
+  </si>
+  <si>
+    <t>None Heal-1</t>
+  </si>
+  <si>
+    <t>None Heal-5</t>
+  </si>
+  <si>
+    <t>Greater5 Attack4</t>
+  </si>
+  <si>
+    <t>Less11 Defence2</t>
+  </si>
+  <si>
+    <t>Less6 Attack5</t>
+  </si>
+  <si>
+    <t>Less6 Defence2</t>
+  </si>
+  <si>
+    <t>Equal3 Defence8</t>
+  </si>
+  <si>
+    <t>Equal6 Defence8</t>
+  </si>
+  <si>
+    <t>Equal9 Defence8 | Equal12 Defence8 | None Attack0</t>
+  </si>
+  <si>
+    <t>None Heal15</t>
+  </si>
+  <si>
+    <t>Equal1 Attack13</t>
+  </si>
+  <si>
+    <t>Equal4 Attack13</t>
+  </si>
+  <si>
+    <t>Equal7 Attack13 | Equal10 Attack13</t>
+  </si>
+  <si>
+    <t>None Heal12</t>
+  </si>
+  <si>
+    <t>Less10 Defence4</t>
   </si>
   <si>
     <t>意图列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>意图1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>意图2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>意图3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以此类推→</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less5 Heal5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal8 Defence3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Attack5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Attack7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less Heal6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal8 Defence4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>意图列表索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>升级后意图列表索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：列表索引会指向意图库里面对应的意图列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辣椒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Notequal Heal6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Notequal Heal7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霉豆腐</t>
+  </si>
+  <si>
+    <t>榴莲汁</t>
+  </si>
+  <si>
+    <t>苦瓜精</t>
+  </si>
+  <si>
+    <t>小块盐</t>
+  </si>
+  <si>
+    <t>小瓶生抽</t>
+  </si>
+  <si>
+    <t>味精</t>
+  </si>
+  <si>
+    <t>胡椒水</t>
+  </si>
+  <si>
+    <t>大碗胡椒水</t>
+  </si>
+  <si>
+    <t>注释：玩家从任何途径获取到素材的时候，从素材库中随机选取一个之前没用抽取过的id对应的素材，因为有些素材可能是只有怪物才有的，所以要做好分离</t>
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：意图用空格分成两部分。第一部分是触发条件。None代表无条件。Equal代表当前时钟值等于某个值才满足。Notequal代表当前时钟值不等于某个值才满足。Less和Greater分别代表当前时钟值小于和大于某个值才满足</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第二部分是指向的动作。目前有三种动作，Attack代表攻击第一个敌方卡牌，Heal和Defence分别代表治疗自身和给自己加护甲。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前的意图条件和行动类型只开发了这些。如果要定义新的意图条件和行动类型，需要说清楚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：玩家从任何途径获取到素材的时候，从素材库中随机选取一个之前没用抽取过的id对应的素材，因为有些素材可能是只有怪物才有的，所以要做好分离</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：这个表描述的是游戏中所有的素材，包括玩家卡牌素材和怪物卡牌素材</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗物意图列表索引</t>
+  </si>
+  <si>
+    <t>素材意图列表索引</t>
+  </si>
+  <si>
+    <t>升级后的素材意图列表索引</t>
+  </si>
+  <si>
+    <t>注释：和素材库一样，这里存的是游戏中所有遗物的定义。如果某个遗物是专门作为怪物遗物，因为他在游戏中不可能被合成成卡牌，因此素材意图置空即可</t>
   </si>
   <si>
     <t>精猪后腿肉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>素材意图列表索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：和素材库一样，这里存的是游戏中所有遗物的定义。如果某个遗物是专门作为怪物遗物，因为他在游戏中不可能被合成成卡牌，因此素材意图置空即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>升级后的素材意图列表索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遗物意图列表索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：关于你这个遗物，你刚开始写的是战斗开始加hp，如果是治疗的话等于是滚木遗物，所以我暂时改成了战斗开始的时候4加盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None RandomDefenceOnStart 4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>注释：同玩家素材池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>卡牌1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>卡牌2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>卡牌3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>卡牌4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗物列表</t>
+  </si>
+  <si>
+    <t>注释：卡牌列填写的数字，代表着组成他们的素材id。遗物列表下填写的数字，代表小怪会携带的所有遗物。两个数字之间用空格分开</t>
+  </si>
+  <si>
+    <t>同样的，当进入小怪战斗后，会抽取一个之前没抽到过的卡牌组</t>
   </si>
   <si>
     <t>1 2 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遗物列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：卡牌列填写的数字，代表着组成他们的素材id。遗物列表下填写的数字，代表小怪会携带的所有遗物。两个数字之间用空格分开</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同样的，当进入小怪战斗后，会抽取一个之前没抽到过的卡牌组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注释：同小怪池</t>
   </si>
   <si>
     <t>同小怪池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注释：同小怪池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>混合肉饼</t>
+  </si>
+  <si>
+    <t>索引ID</t>
+  </si>
+  <si>
+    <t>合成表</t>
+  </si>
+  <si>
+    <t>合成物</t>
+  </si>
+  <si>
+    <t>N2.1</t>
+  </si>
+  <si>
+    <t>香菇*1</t>
+  </si>
+  <si>
+    <t>n2.2</t>
+  </si>
+  <si>
+    <t>任意肉*1</t>
+  </si>
+  <si>
+    <t>N2.3</t>
+  </si>
+  <si>
+    <t>糊的肉*1</t>
+  </si>
+  <si>
+    <t>N2.4</t>
+  </si>
+  <si>
+    <t>任意水*1+盐*1</t>
+  </si>
+  <si>
+    <t>盐水</t>
+  </si>
+  <si>
+    <t>N2.5</t>
+  </si>
+  <si>
+    <t>盐水*1+任意水*1</t>
+  </si>
+  <si>
+    <t>N2.6</t>
+  </si>
+  <si>
+    <t>任意2稀有度及以上的水*1+盐*1</t>
+  </si>
+  <si>
+    <t>N2.7</t>
+  </si>
+  <si>
+    <t>N2.8</t>
+  </si>
+  <si>
+    <t>N2.9</t>
+  </si>
+  <si>
+    <t>N2.10</t>
+  </si>
+  <si>
+    <t>N2.11</t>
+  </si>
+  <si>
+    <t>N2.12</t>
+  </si>
+  <si>
+    <t>N2.13</t>
+  </si>
+  <si>
+    <t>N2.14</t>
+  </si>
+  <si>
+    <t>N2.15</t>
+  </si>
+  <si>
+    <t>N2.16</t>
+  </si>
+  <si>
+    <t>N2.17</t>
+  </si>
+  <si>
+    <t>N2.18</t>
+  </si>
+  <si>
+    <t>N2.19</t>
+  </si>
+  <si>
+    <t>N2.20</t>
+  </si>
+  <si>
+    <t>N2.21</t>
+  </si>
+  <si>
+    <t>N2.22</t>
+  </si>
+  <si>
+    <t>N2.23</t>
+  </si>
+  <si>
+    <t>N2.24</t>
+  </si>
+  <si>
+    <t>N2.25</t>
+  </si>
+  <si>
+    <t>N2.26</t>
+  </si>
+  <si>
+    <t>N2.27</t>
+  </si>
+  <si>
+    <t>N2.28</t>
+  </si>
+  <si>
+    <t>N2.29</t>
+  </si>
+  <si>
+    <t>N2.30</t>
+  </si>
+  <si>
+    <t>N2.31</t>
+  </si>
+  <si>
+    <t>N2.32</t>
+  </si>
+  <si>
+    <t>角色名字</t>
+  </si>
+  <si>
+    <t>升级所需经验</t>
+  </si>
+  <si>
+    <t>角色星级</t>
+  </si>
+  <si>
+    <t>背包里显示的图标</t>
+  </si>
+  <si>
+    <t>升级路径</t>
+  </si>
+  <si>
+    <t>特殊机制与加成</t>
+  </si>
+  <si>
+    <t>N1.0</t>
+  </si>
+  <si>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;2-&gt;3-&gt;3</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>N1.1</t>
+  </si>
+  <si>
+    <t>无-&gt;无&gt;无-&gt;无</t>
+  </si>
+  <si>
+    <t>猪腿煲汤</t>
+  </si>
+  <si>
+    <t>N1.2</t>
+  </si>
+  <si>
+    <t>无-&gt;hp+3-&gt;无-&gt;无</t>
+  </si>
+  <si>
+    <t>战斗开始获得十格挡</t>
+  </si>
+  <si>
+    <t>特级精品猪油+精品猪后腿肉+咸水</t>
+  </si>
+  <si>
+    <t>海洋混混浓汤</t>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;2-&gt;3-&gt;5</t>
+  </si>
+  <si>
+    <t>N1.3</t>
+  </si>
+  <si>
+    <t>无-&gt;hp+3-&gt;hp+3-&gt;hp+9</t>
+  </si>
+  <si>
+    <t>hp+29,增加意图：=2/5/8/11,打2*4</t>
+  </si>
+  <si>
+    <t>海藻水+海藻气泡+海藻团块</t>
+  </si>
+  <si>
+    <t>N1.4</t>
+  </si>
+  <si>
+    <t>N1.5</t>
+  </si>
+  <si>
+    <t>N1.6</t>
+  </si>
+  <si>
+    <t>N1.7</t>
+  </si>
+  <si>
+    <t>N1.8</t>
+  </si>
+  <si>
+    <t>N1.9</t>
+  </si>
+  <si>
+    <t>N1.10</t>
+  </si>
+  <si>
+    <t>N1.11</t>
+  </si>
+  <si>
+    <t>N1.12</t>
+  </si>
+  <si>
+    <t>N1.13</t>
+  </si>
+  <si>
+    <t>N1.14</t>
+  </si>
+  <si>
+    <t>N1.15</t>
+  </si>
+  <si>
+    <t>N1.16</t>
+  </si>
+  <si>
+    <t>N1.17</t>
+  </si>
+  <si>
+    <t>N1.18</t>
+  </si>
+  <si>
+    <t>N1.19</t>
+  </si>
+  <si>
+    <t>N1.20</t>
+  </si>
+  <si>
+    <t>N1.21</t>
+  </si>
+  <si>
+    <t>N1.22</t>
+  </si>
+  <si>
+    <t>N1.23</t>
+  </si>
+  <si>
+    <t>N1.24</t>
+  </si>
+  <si>
+    <t>N1.25</t>
+  </si>
+  <si>
+    <t>N1.26</t>
+  </si>
+  <si>
+    <t>N1.27</t>
+  </si>
+  <si>
+    <t>N1.28</t>
+  </si>
+  <si>
+    <t>N1.29</t>
+  </si>
+  <si>
+    <t>N1.30</t>
+  </si>
+  <si>
+    <t>N1.31</t>
+  </si>
+  <si>
+    <t>N1.32</t>
+  </si>
+  <si>
+    <t>N1.33</t>
+  </si>
+  <si>
+    <t>N1.34</t>
+  </si>
+  <si>
+    <t>N1.35</t>
+  </si>
+  <si>
+    <t>N1.36</t>
+  </si>
+  <si>
+    <t>N1.37</t>
+  </si>
+  <si>
+    <t>N1.38</t>
+  </si>
+  <si>
+    <t>N1.39</t>
+  </si>
+  <si>
+    <t>N1.40</t>
+  </si>
+  <si>
+    <t>N1.41</t>
+  </si>
+  <si>
+    <t>N1.42</t>
+  </si>
+  <si>
+    <t>N1.43</t>
+  </si>
+  <si>
+    <t>N1.44</t>
+  </si>
+  <si>
+    <t>N1.45</t>
+  </si>
+  <si>
+    <t>N1.46</t>
+  </si>
+  <si>
+    <t>N1.47</t>
+  </si>
+  <si>
+    <t>N1.48</t>
+  </si>
+  <si>
+    <t>N1.49</t>
+  </si>
+  <si>
+    <t>N1.50</t>
+  </si>
+  <si>
+    <t>N1.51</t>
+  </si>
+  <si>
+    <t>N1.52</t>
+  </si>
+  <si>
+    <t>N1.53</t>
+  </si>
+  <si>
+    <t>N1.54</t>
+  </si>
+  <si>
+    <t>N1.55</t>
+  </si>
+  <si>
+    <t>N1.56</t>
+  </si>
+  <si>
+    <t>N1.57</t>
+  </si>
+  <si>
+    <t>N1.58</t>
+  </si>
+  <si>
+    <t>N1.59</t>
+  </si>
+  <si>
+    <t>N1.60</t>
+  </si>
+  <si>
+    <t>N1.61</t>
+  </si>
+  <si>
+    <t>N1.62</t>
+  </si>
+  <si>
+    <t>N1.63</t>
+  </si>
+  <si>
+    <t>N1.64</t>
+  </si>
+  <si>
+    <t>N1.65</t>
+  </si>
+  <si>
+    <t>N1.66</t>
+  </si>
+  <si>
+    <t>N1.67</t>
+  </si>
+  <si>
+    <t>N1.68</t>
+  </si>
+  <si>
+    <t>N1.69</t>
+  </si>
+  <si>
+    <t>N1.70</t>
+  </si>
+  <si>
+    <t>N1.71</t>
+  </si>
+  <si>
+    <t>N1.72</t>
+  </si>
+  <si>
+    <t>N1.73</t>
+  </si>
+  <si>
+    <t>N1.74</t>
+  </si>
+  <si>
+    <t>N1.75</t>
+  </si>
+  <si>
+    <t>N1.76</t>
+  </si>
+  <si>
+    <t>N1.77</t>
+  </si>
+  <si>
+    <t>N1.78</t>
+  </si>
+  <si>
+    <t>N1.79</t>
+  </si>
+  <si>
+    <t>N1.80</t>
+  </si>
+  <si>
+    <t>N1.81</t>
+  </si>
+  <si>
+    <t>N1.82</t>
+  </si>
+  <si>
+    <t>N1.83</t>
+  </si>
+  <si>
+    <t>N1.84</t>
+  </si>
+  <si>
+    <t>N1.85</t>
+  </si>
+  <si>
+    <t>N1.86</t>
+  </si>
+  <si>
+    <t>N1.87</t>
+  </si>
+  <si>
+    <t>N1.88</t>
+  </si>
+  <si>
+    <t>N1.89</t>
+  </si>
+  <si>
+    <t>N1.90</t>
+  </si>
+  <si>
+    <t>N1.91</t>
+  </si>
+  <si>
+    <t>N1.92</t>
+  </si>
+  <si>
+    <t>N1.93</t>
+  </si>
+  <si>
+    <t>N1.94</t>
+  </si>
+  <si>
+    <t>N1.95</t>
+  </si>
+  <si>
+    <t>N1.96</t>
+  </si>
+  <si>
+    <t>N1.97</t>
+  </si>
+  <si>
+    <t>N1.98</t>
+  </si>
+  <si>
+    <t>N1.99</t>
+  </si>
+  <si>
+    <t>N1.100</t>
+  </si>
+  <si>
+    <t>N1.101</t>
+  </si>
+  <si>
+    <t>N1.102</t>
+  </si>
+  <si>
+    <t>N1.103</t>
+  </si>
+  <si>
+    <t>N1.104</t>
+  </si>
+  <si>
+    <t>N1.105</t>
+  </si>
+  <si>
+    <t>N1.106</t>
+  </si>
+  <si>
+    <t>N1.107</t>
+  </si>
+  <si>
+    <t>N1.108</t>
+  </si>
+  <si>
+    <t>N1.109</t>
+  </si>
+  <si>
+    <t>N1.110</t>
+  </si>
+  <si>
+    <t>N1.111</t>
+  </si>
+  <si>
+    <t>N1.112</t>
+  </si>
+  <si>
+    <t>N1.113</t>
+  </si>
+  <si>
+    <t>N1.114</t>
+  </si>
+  <si>
+    <t>N1.115</t>
+  </si>
+  <si>
+    <t>N1.116</t>
+  </si>
+  <si>
+    <t>N1.117</t>
+  </si>
+  <si>
+    <t>N1.118</t>
+  </si>
+  <si>
+    <t>N1.119</t>
+  </si>
+  <si>
+    <t>N1.120</t>
+  </si>
+  <si>
+    <t>N1.121</t>
+  </si>
+  <si>
+    <t>N1.122</t>
+  </si>
+  <si>
+    <t>N1.123</t>
+  </si>
+  <si>
+    <t>N1.124</t>
+  </si>
+  <si>
+    <t>N1.125</t>
+  </si>
+  <si>
+    <t>N1.126</t>
+  </si>
+  <si>
+    <t>N1.127</t>
+  </si>
+  <si>
+    <t>N1.128</t>
+  </si>
+  <si>
+    <t>N1.129</t>
+  </si>
+  <si>
+    <t>N1.130</t>
+  </si>
+  <si>
+    <t>N1.131</t>
+  </si>
+  <si>
+    <t>N1.132</t>
+  </si>
+  <si>
+    <t>N1.133</t>
+  </si>
+  <si>
+    <t>N1.134</t>
+  </si>
+  <si>
+    <t>N1.135</t>
+  </si>
+  <si>
+    <t>N1.136</t>
+  </si>
+  <si>
+    <t>N1.137</t>
+  </si>
+  <si>
+    <t>N1.138</t>
+  </si>
+  <si>
+    <t>N1.139</t>
+  </si>
+  <si>
+    <t>N1.140</t>
+  </si>
+  <si>
+    <t>N1.141</t>
+  </si>
+  <si>
+    <t>N1.142</t>
+  </si>
+  <si>
+    <t>N1.143</t>
+  </si>
+  <si>
+    <t>N1.144</t>
+  </si>
+  <si>
+    <t>N1.145</t>
+  </si>
+  <si>
+    <t>N1.146</t>
+  </si>
+  <si>
+    <t>N1.147</t>
+  </si>
+  <si>
+    <t>N1.148</t>
+  </si>
+  <si>
+    <t>N1.149</t>
+  </si>
+  <si>
+    <t>N1.150</t>
+  </si>
+  <si>
+    <t>N1.151</t>
+  </si>
+  <si>
+    <t>N1.152</t>
+  </si>
+  <si>
+    <t>N1.153</t>
+  </si>
+  <si>
+    <t>N1.154</t>
+  </si>
+  <si>
+    <t>N1.155</t>
+  </si>
+  <si>
+    <t>N1.156</t>
+  </si>
+  <si>
+    <t>N1.157</t>
+  </si>
+  <si>
+    <t>N1.158</t>
+  </si>
+  <si>
+    <t>N1.159</t>
+  </si>
+  <si>
+    <t>N1.160</t>
+  </si>
+  <si>
+    <t>N1.161</t>
+  </si>
+  <si>
+    <t>N1.162</t>
+  </si>
+  <si>
+    <t>N1.163</t>
+  </si>
+  <si>
+    <t>N1.164</t>
+  </si>
+  <si>
+    <t>N1.165</t>
+  </si>
+  <si>
+    <t>N1.166</t>
+  </si>
+  <si>
+    <t>N1.167</t>
+  </si>
+  <si>
+    <t>N1.168</t>
+  </si>
+  <si>
+    <t>N1.169</t>
+  </si>
+  <si>
+    <t>N1.170</t>
+  </si>
+  <si>
+    <t>N1.171</t>
+  </si>
+  <si>
+    <t>N1.172</t>
+  </si>
+  <si>
+    <t>N1.173</t>
+  </si>
+  <si>
+    <t>N1.174</t>
+  </si>
+  <si>
+    <t>N1.175</t>
+  </si>
+  <si>
+    <t>N1.176</t>
+  </si>
+  <si>
+    <t>N1.177</t>
+  </si>
+  <si>
+    <t>N1.178</t>
+  </si>
+  <si>
+    <t>N1.179</t>
+  </si>
+  <si>
+    <t>N1.180</t>
+  </si>
+  <si>
+    <t>N1.181</t>
+  </si>
+  <si>
+    <t>N1.182</t>
+  </si>
+  <si>
+    <t>N1.183</t>
+  </si>
+  <si>
+    <t>N1.184</t>
+  </si>
+  <si>
+    <t>N1.185</t>
+  </si>
+  <si>
+    <t>N1.186</t>
+  </si>
+  <si>
+    <t>N1.187</t>
+  </si>
+  <si>
+    <t>N1.188</t>
+  </si>
+  <si>
+    <t>N1.189</t>
+  </si>
+  <si>
+    <t>N1.190</t>
+  </si>
+  <si>
+    <t>N1.191</t>
+  </si>
+  <si>
+    <t>N1.192</t>
+  </si>
+  <si>
+    <t>N1.193</t>
+  </si>
+  <si>
+    <t>N1.194</t>
+  </si>
+  <si>
+    <t>N1.195</t>
+  </si>
+  <si>
+    <t>N1.196</t>
+  </si>
+  <si>
+    <t>N1.197</t>
+  </si>
+  <si>
+    <t>N1.198</t>
+  </si>
+  <si>
+    <t>N1.199</t>
+  </si>
+  <si>
+    <t>N1.200</t>
+  </si>
+  <si>
+    <t>N1.201</t>
+  </si>
+  <si>
+    <t>N1.202</t>
+  </si>
+  <si>
+    <t>N1.203</t>
+  </si>
+  <si>
+    <t>N1.204</t>
+  </si>
+  <si>
+    <t>N1.205</t>
+  </si>
+  <si>
+    <t>N1.206</t>
+  </si>
+  <si>
+    <t>N1.207</t>
+  </si>
+  <si>
+    <t>N1.208</t>
+  </si>
+  <si>
+    <t>N1.209</t>
+  </si>
+  <si>
+    <t>N1.210</t>
+  </si>
+  <si>
+    <t>N1.211</t>
+  </si>
+  <si>
+    <t>N1.212</t>
+  </si>
+  <si>
+    <t>N1.213</t>
+  </si>
+  <si>
+    <t>N1.214</t>
+  </si>
+  <si>
+    <t>N1.215</t>
+  </si>
+  <si>
+    <t>N1.216</t>
+  </si>
+  <si>
+    <t>N1.217</t>
+  </si>
+  <si>
+    <t>N1.218</t>
+  </si>
+  <si>
+    <t>N1.219</t>
+  </si>
+  <si>
+    <t>N1.220</t>
+  </si>
+  <si>
+    <t>N1.221</t>
+  </si>
+  <si>
+    <t>N1.222</t>
+  </si>
+  <si>
+    <t>N1.223</t>
+  </si>
+  <si>
+    <t>N1.224</t>
+  </si>
+  <si>
+    <t>N1.225</t>
+  </si>
+  <si>
+    <t>N1.226</t>
+  </si>
+  <si>
+    <t>N1.227</t>
+  </si>
+  <si>
+    <t>N1.228</t>
+  </si>
+  <si>
+    <t>N1.229</t>
+  </si>
+  <si>
+    <t>N1.230</t>
+  </si>
+  <si>
+    <t>N1.231</t>
+  </si>
+  <si>
+    <t>N1.232</t>
+  </si>
+  <si>
+    <t>N1.233</t>
+  </si>
+  <si>
+    <t>N1.234</t>
+  </si>
+  <si>
+    <t>N1.235</t>
+  </si>
+  <si>
+    <t>N1.236</t>
+  </si>
+  <si>
+    <t>N1.237</t>
+  </si>
+  <si>
+    <t>N1.238</t>
+  </si>
+  <si>
+    <t>N1.239</t>
+  </si>
+  <si>
+    <t>N1.240</t>
+  </si>
+  <si>
+    <t>N1.241</t>
+  </si>
+  <si>
+    <t>N1.242</t>
+  </si>
+  <si>
+    <t>N1.243</t>
+  </si>
+  <si>
+    <t>N1.244</t>
+  </si>
+  <si>
+    <t>N1.245</t>
+  </si>
+  <si>
+    <t>N1.246</t>
+  </si>
+  <si>
+    <t>N1.247</t>
+  </si>
+  <si>
+    <t>N1.248</t>
+  </si>
+  <si>
+    <t>N1.249</t>
+  </si>
+  <si>
+    <t>N1.250</t>
+  </si>
+  <si>
+    <t>N1.251</t>
+  </si>
+  <si>
+    <t>N1.252</t>
+  </si>
+  <si>
+    <t>N1.253</t>
+  </si>
+  <si>
+    <t>N1.254</t>
+  </si>
+  <si>
+    <t>N1.255</t>
+  </si>
+  <si>
+    <t>N1.256</t>
+  </si>
+  <si>
+    <t>N1.257</t>
+  </si>
+  <si>
+    <t>N1.258</t>
+  </si>
+  <si>
+    <t>N1.259</t>
+  </si>
+  <si>
+    <t>N1.260</t>
+  </si>
+  <si>
+    <t>N1.261</t>
+  </si>
+  <si>
+    <t>N1.262</t>
+  </si>
+  <si>
+    <t>N1.263</t>
+  </si>
+  <si>
+    <t>N1.264</t>
+  </si>
+  <si>
+    <t>N1.265</t>
+  </si>
+  <si>
+    <t>N1.266</t>
+  </si>
+  <si>
+    <t>N1.267</t>
+  </si>
+  <si>
+    <t>N1.268</t>
+  </si>
+  <si>
+    <t>N1.269</t>
+  </si>
+  <si>
+    <t>N1.270</t>
+  </si>
+  <si>
+    <t>N1.271</t>
+  </si>
+  <si>
+    <t>N1.272</t>
+  </si>
+  <si>
+    <t>N1.273</t>
+  </si>
+  <si>
+    <t>N1.274</t>
+  </si>
+  <si>
+    <t>N1.275</t>
+  </si>
+  <si>
+    <t>N1.276</t>
+  </si>
+  <si>
+    <t>N1.277</t>
+  </si>
+  <si>
+    <t>N1.278</t>
+  </si>
+  <si>
+    <t>N1.279</t>
+  </si>
+  <si>
+    <t>N1.280</t>
+  </si>
+  <si>
+    <t>N1.281</t>
+  </si>
+  <si>
+    <t>N1.282</t>
+  </si>
+  <si>
+    <t>N1.283</t>
+  </si>
+  <si>
+    <t>N1.284</t>
+  </si>
+  <si>
+    <t>N1.285</t>
+  </si>
+  <si>
+    <t>N1.286</t>
+  </si>
+  <si>
+    <t>N1.287</t>
+  </si>
+  <si>
+    <t>N1.288</t>
+  </si>
+  <si>
+    <t>N1.289</t>
+  </si>
+  <si>
+    <t>N1.290</t>
+  </si>
+  <si>
+    <t>N1.291</t>
+  </si>
+  <si>
+    <t>N1.292</t>
+  </si>
+  <si>
+    <t>N1.293</t>
+  </si>
+  <si>
+    <t>N1.294</t>
+  </si>
+  <si>
+    <t>N1.295</t>
+  </si>
+  <si>
+    <t>N1.296</t>
+  </si>
+  <si>
+    <t>N1.297</t>
+  </si>
+  <si>
+    <t>N1.298</t>
+  </si>
+  <si>
+    <t>N1.299</t>
+  </si>
+  <si>
+    <t>N1.300</t>
+  </si>
+  <si>
+    <t>N1.301</t>
+  </si>
+  <si>
+    <t>N1.302</t>
+  </si>
+  <si>
+    <t>N1.303</t>
+  </si>
+  <si>
+    <t>N1.304</t>
+  </si>
+  <si>
+    <t>N1.305</t>
+  </si>
+  <si>
+    <t>N1.306</t>
+  </si>
+  <si>
+    <t>N1.307</t>
+  </si>
+  <si>
+    <t>N1.308</t>
+  </si>
+  <si>
+    <t>N1.309</t>
+  </si>
+  <si>
+    <t>N1.310</t>
+  </si>
+  <si>
+    <t>N1.311</t>
+  </si>
+  <si>
+    <t>N1.312</t>
+  </si>
+  <si>
+    <t>N1.313</t>
+  </si>
+  <si>
+    <t>N1.314</t>
+  </si>
+  <si>
+    <t>N1.315</t>
+  </si>
+  <si>
+    <t>N1.316</t>
+  </si>
+  <si>
+    <t>N1.317</t>
+  </si>
+  <si>
+    <t>N1.318</t>
+  </si>
+  <si>
+    <t>N1.319</t>
+  </si>
+  <si>
+    <t>N1.320</t>
+  </si>
+  <si>
+    <t>N1.321</t>
+  </si>
+  <si>
+    <t>N1.322</t>
+  </si>
+  <si>
+    <t>N1.323</t>
+  </si>
+  <si>
+    <t>N1.324</t>
+  </si>
+  <si>
+    <t>N1.325</t>
+  </si>
+  <si>
+    <t>N1.326</t>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack0 | Equal12 Attack0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -263,7 +1591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -276,6 +1604,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,18 +1891,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="24.44140625" style="2" customWidth="1"/>
     <col min="6" max="7" width="20.21875" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.33203125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="9" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -582,24 +1919,24 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>46</v>
+      <c r="B2" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="2">
         <v>5</v>
@@ -618,13 +1955,10 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
         <v>3</v>
       </c>
       <c r="E3" s="2">
@@ -638,6 +1972,12 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
       <c r="E4" s="2">
         <v>5</v>
       </c>
@@ -649,6 +1989,12 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5">
+        <v>5</v>
+      </c>
       <c r="E5" s="2">
         <v>7</v>
       </c>
@@ -660,6 +2006,12 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
       <c r="E6" s="2">
         <v>9</v>
       </c>
@@ -668,6 +2020,15 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
@@ -676,6 +2037,15 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
@@ -684,6 +2054,15 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5</v>
+      </c>
       <c r="E9" s="2">
         <v>15</v>
       </c>
@@ -692,6 +2071,15 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
       <c r="E10" s="2">
         <v>17</v>
       </c>
@@ -700,6 +2088,15 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
@@ -708,6 +2105,15 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
       <c r="E12" s="2">
         <v>21</v>
       </c>
@@ -716,6 +2122,15 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
       <c r="E13" s="2">
         <v>23</v>
       </c>
@@ -724,6 +2139,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5">
+        <v>5</v>
+      </c>
       <c r="E14" s="2">
         <v>25</v>
       </c>
@@ -732,6 +2156,15 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5">
+        <v>6</v>
+      </c>
       <c r="E15" s="2">
         <v>27</v>
       </c>
@@ -740,6 +2173,15 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5">
+        <v>10</v>
+      </c>
       <c r="E16" s="2">
         <v>29</v>
       </c>
@@ -747,7 +2189,16 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
       <c r="E17" s="2">
         <v>31</v>
       </c>
@@ -755,7 +2206,16 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5</v>
+      </c>
       <c r="E18" s="2">
         <v>33</v>
       </c>
@@ -763,7 +2223,16 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
       <c r="E19" s="2">
         <v>35</v>
       </c>
@@ -771,7 +2240,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
       <c r="E20" s="2">
         <v>37</v>
       </c>
@@ -779,7 +2254,16 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-2</v>
+      </c>
       <c r="E21" s="2">
         <v>39</v>
       </c>
@@ -787,91 +2271,2647 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-5</v>
+      </c>
       <c r="E22" s="2">
         <v>41</v>
       </c>
       <c r="F22" s="2">
         <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5">
+        <v>43</v>
+      </c>
+      <c r="F23" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="5">
+        <v>10</v>
+      </c>
+      <c r="E24" s="5">
+        <v>45</v>
+      </c>
+      <c r="F24" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5</v>
+      </c>
+      <c r="E25" s="5">
+        <v>47</v>
+      </c>
+      <c r="F25" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="5">
+        <v>10</v>
+      </c>
+      <c r="E26" s="5">
+        <v>49</v>
+      </c>
+      <c r="F26" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="5">
+        <v>10</v>
+      </c>
+      <c r="E27" s="5">
+        <v>51</v>
+      </c>
+      <c r="F27" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="5">
+        <v>5</v>
+      </c>
+      <c r="E28" s="5">
+        <v>53</v>
+      </c>
+      <c r="F28" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="5">
+        <v>15</v>
+      </c>
+      <c r="E29" s="5">
+        <v>55</v>
+      </c>
+      <c r="F29" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="5">
+        <v>12</v>
+      </c>
+      <c r="E30" s="5">
+        <v>57</v>
+      </c>
+      <c r="F30" s="5">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:H327"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>193</v>
+      </c>
+      <c r="E17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>208</v>
+      </c>
+      <c r="E32" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>210</v>
+      </c>
+      <c r="E34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>212</v>
+      </c>
+      <c r="E36" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>213</v>
+      </c>
+      <c r="E37" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>214</v>
+      </c>
+      <c r="E38" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>216</v>
+      </c>
+      <c r="E40" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>217</v>
+      </c>
+      <c r="E41" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>218</v>
+      </c>
+      <c r="E42" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>220</v>
+      </c>
+      <c r="E44" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>221</v>
+      </c>
+      <c r="E45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>222</v>
+      </c>
+      <c r="E46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>225</v>
+      </c>
+      <c r="E49" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>227</v>
+      </c>
+      <c r="E51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>228</v>
+      </c>
+      <c r="E52" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>229</v>
+      </c>
+      <c r="E53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>230</v>
+      </c>
+      <c r="E54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>231</v>
+      </c>
+      <c r="E55" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>232</v>
+      </c>
+      <c r="E56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>233</v>
+      </c>
+      <c r="E57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>234</v>
+      </c>
+      <c r="E58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>235</v>
+      </c>
+      <c r="E59" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>236</v>
+      </c>
+      <c r="E60" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>237</v>
+      </c>
+      <c r="E61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>238</v>
+      </c>
+      <c r="E62" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>239</v>
+      </c>
+      <c r="E63" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>241</v>
+      </c>
+      <c r="E64" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>242</v>
+      </c>
+      <c r="E65" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>243</v>
+      </c>
+      <c r="E66" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>244</v>
+      </c>
+      <c r="E67" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>245</v>
+      </c>
+      <c r="E68" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>246</v>
+      </c>
+      <c r="E69" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>247</v>
+      </c>
+      <c r="E70" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>248</v>
+      </c>
+      <c r="E71" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>249</v>
+      </c>
+      <c r="E72" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>250</v>
+      </c>
+      <c r="E73" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>251</v>
+      </c>
+      <c r="E74" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>252</v>
+      </c>
+      <c r="E75" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>253</v>
+      </c>
+      <c r="E76" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>254</v>
+      </c>
+      <c r="E77" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>255</v>
+      </c>
+      <c r="E78" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>256</v>
+      </c>
+      <c r="E79" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>257</v>
+      </c>
+      <c r="E80" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>258</v>
+      </c>
+      <c r="E81" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>259</v>
+      </c>
+      <c r="E82" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>260</v>
+      </c>
+      <c r="E83" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>261</v>
+      </c>
+      <c r="E84" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>262</v>
+      </c>
+      <c r="E85" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>263</v>
+      </c>
+      <c r="E86" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>264</v>
+      </c>
+      <c r="E87" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>265</v>
+      </c>
+      <c r="E88" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>266</v>
+      </c>
+      <c r="E89" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>267</v>
+      </c>
+      <c r="E90" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>268</v>
+      </c>
+      <c r="E91" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>269</v>
+      </c>
+      <c r="E92" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>270</v>
+      </c>
+      <c r="E93" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>271</v>
+      </c>
+      <c r="E94" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>272</v>
+      </c>
+      <c r="E95" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>273</v>
+      </c>
+      <c r="E96" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>274</v>
+      </c>
+      <c r="E97" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>275</v>
+      </c>
+      <c r="E98" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>276</v>
+      </c>
+      <c r="E99" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>277</v>
+      </c>
+      <c r="E100" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>278</v>
+      </c>
+      <c r="E101" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>279</v>
+      </c>
+      <c r="E102" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>280</v>
+      </c>
+      <c r="E103" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>281</v>
+      </c>
+      <c r="E104" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>282</v>
+      </c>
+      <c r="E105" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>283</v>
+      </c>
+      <c r="E106" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>284</v>
+      </c>
+      <c r="E107" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>285</v>
+      </c>
+      <c r="E108" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>286</v>
+      </c>
+      <c r="E109" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>287</v>
+      </c>
+      <c r="E110" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>288</v>
+      </c>
+      <c r="E111" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>289</v>
+      </c>
+      <c r="E112" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>290</v>
+      </c>
+      <c r="E113" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>291</v>
+      </c>
+      <c r="E114" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>292</v>
+      </c>
+      <c r="E115" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>293</v>
+      </c>
+      <c r="E116" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>294</v>
+      </c>
+      <c r="E117" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>295</v>
+      </c>
+      <c r="E118" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>296</v>
+      </c>
+      <c r="E119" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>297</v>
+      </c>
+      <c r="E120" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>298</v>
+      </c>
+      <c r="E121" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>299</v>
+      </c>
+      <c r="E122" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>300</v>
+      </c>
+      <c r="E123" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>301</v>
+      </c>
+      <c r="E124" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>302</v>
+      </c>
+      <c r="E125" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>303</v>
+      </c>
+      <c r="E126" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>304</v>
+      </c>
+      <c r="E127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E128" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>306</v>
+      </c>
+      <c r="E129" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>307</v>
+      </c>
+      <c r="E130" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>308</v>
+      </c>
+      <c r="E131" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>309</v>
+      </c>
+      <c r="E132" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>310</v>
+      </c>
+      <c r="E133" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>311</v>
+      </c>
+      <c r="E134" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>312</v>
+      </c>
+      <c r="E135" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>313</v>
+      </c>
+      <c r="E136" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>314</v>
+      </c>
+      <c r="E137" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>315</v>
+      </c>
+      <c r="E138" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>316</v>
+      </c>
+      <c r="E139" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>317</v>
+      </c>
+      <c r="E140" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>318</v>
+      </c>
+      <c r="E141" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>319</v>
+      </c>
+      <c r="E142" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>320</v>
+      </c>
+      <c r="E143" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>321</v>
+      </c>
+      <c r="E144" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>322</v>
+      </c>
+      <c r="E145" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>323</v>
+      </c>
+      <c r="E146" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>324</v>
+      </c>
+      <c r="E147" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>325</v>
+      </c>
+      <c r="E148" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>326</v>
+      </c>
+      <c r="E149" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>327</v>
+      </c>
+      <c r="E150" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>328</v>
+      </c>
+      <c r="E151" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>329</v>
+      </c>
+      <c r="E152" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>330</v>
+      </c>
+      <c r="E153" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>331</v>
+      </c>
+      <c r="E154" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>332</v>
+      </c>
+      <c r="E155" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>333</v>
+      </c>
+      <c r="E156" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>334</v>
+      </c>
+      <c r="E157" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>335</v>
+      </c>
+      <c r="E158" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>336</v>
+      </c>
+      <c r="E159" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>337</v>
+      </c>
+      <c r="E160" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>338</v>
+      </c>
+      <c r="E161" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>339</v>
+      </c>
+      <c r="E162" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>340</v>
+      </c>
+      <c r="E163" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E164" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E165" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E166" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E167" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E168" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E169" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E170" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E171" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E172" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E173" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E174" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E175" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E176" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E177" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E178" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E179" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E180" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E181" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E182" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E183" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E184" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E185" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E186" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E187" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E188" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E189" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E190" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E191" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E192" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E193" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E194" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E195" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="196" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E196" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="197" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E197" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E198" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="199" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E199" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="200" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E200" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="201" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E201" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="202" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E202" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="203" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E203" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="204" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E204" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="205" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E205" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="206" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E206" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="207" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E207" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="208" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E208" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E209" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E210" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E211" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E212" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E213" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E214" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E215" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E216" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E218" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E219" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E220" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E221" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E222" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E223" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E224" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E225" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E226" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E227" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E228" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E229" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E230" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E231" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E232" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E233" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E234" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E235" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E236" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E237" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E238" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E239" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E240" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E241" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E242" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E243" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E244" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E245" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E246" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E247" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E248" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E249" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E250" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E251" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E252" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E253" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E254" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E255" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E256" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E257" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E258" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E259" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E260" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E261" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E262" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E263" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E264" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E265" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E266" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E267" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E268" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E269" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E270" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E271" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E272" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E273" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E274" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E275" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E276" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E277" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E278" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E279" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="280" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E280" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="281" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E281" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="282" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E282" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="283" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E283" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="284" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E284" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="285" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E285" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="286" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E286" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="287" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E287" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="288" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E288" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="289" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E289" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="290" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E290" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="291" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E291" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="292" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E292" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="293" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E293" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="294" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E294" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="295" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E295" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="296" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E296" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="297" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E297" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="298" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E298" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="299" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E299" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="300" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E300" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="301" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E301" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="302" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E302" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="303" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E303" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="304" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E304" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="305" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E305" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="306" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E306" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="307" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E307" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="308" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E308" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="309" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E309" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="310" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E310" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="311" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E311" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="312" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E312" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="313" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E313" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="314" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E314" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="315" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E315" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="316" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E316" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="317" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E317" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="318" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E318" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="319" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E319" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="320" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E320" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="321" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E321" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="322" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E322" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="323" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E323" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="324" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E324" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="325" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E325" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="326" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E326" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="327" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E327" t="s">
+        <v>504</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919218B-E131-4143-AB50-79A72E51C644}">
-  <dimension ref="A1:L6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16" style="2" customWidth="1"/>
-    <col min="6" max="8" width="9" style="2"/>
+    <col min="5" max="5" width="24.77734375" style="2" customWidth="1"/>
+    <col min="6" max="8" width="9" style="2" customWidth="1"/>
     <col min="9" max="9" width="20.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2"/>
+    <col min="10" max="10" width="9" style="2" customWidth="1"/>
     <col min="11" max="11" width="20.21875" style="2" customWidth="1"/>
     <col min="12" max="12" width="17.77734375" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="13" max="14" width="9" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="138" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -879,7 +4919,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -887,7 +4927,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -895,7 +4944,611 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
         <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" t="s">
+        <v>81</v>
+      </c>
+      <c r="E53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -905,8 +5558,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1074A89F-2652-443D-BB3C-BB014D324722}">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -917,12 +5570,95 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -932,46 +5668,254 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3568C53C-0336-4118-8C36-0FB9EB26128F}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.44140625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="3" max="4" width="9" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -981,38 +5925,39 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F438E8A-FCA7-40DE-9EE5-7F73BB8BE90C}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="23.77734375" style="1" customWidth="1"/>
     <col min="7" max="7" width="24.88671875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1020,13 +5965,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="C2" s="1">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>59</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="5">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1036,8 +5990,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B514FEB-CB79-4116-8D56-FF07CAAEE429}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.44140625" customWidth="1"/>
@@ -1048,12 +6002,23 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1063,41 +6028,42 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D2A9B2-6CD1-4D46-9EC7-7CDE15559BEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="9" style="3"/>
+    <col min="1" max="5" width="9" style="3" customWidth="1"/>
     <col min="6" max="6" width="15" style="3" customWidth="1"/>
     <col min="7" max="7" width="25.44140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="15.21875" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3"/>
+    <col min="9" max="10" width="9" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="69" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1105,10 +6071,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -1121,7 +6087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5139357-4865-410A-B8A0-193B24F73826}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1130,22 +6096,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="G1" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1160,31 +6126,31 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE6E2BC-2530-45EC-B0CD-4849549B7D87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">

--- a/Assets/Documents/全局配置表.xlsx
+++ b/Assets/Documents/全局配置表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\何睿豪\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Projects\Unity\MagicSoup\Assets\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A8946C-2FCF-4FF7-9EDE-EA3272574CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027754AD-6F77-4402-9A2E-C1AA62A63871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="素材库" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,12 @@
     <sheet name="合成表" sheetId="10" r:id="rId10"/>
     <sheet name="角色" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1892,20 +1897,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="18" style="6" customWidth="1"/>
     <col min="3" max="3" width="9" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.44140625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="20.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.4140625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="20.25" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.33203125" style="2" customWidth="1"/>
     <col min="9" max="10" width="9" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="55.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1931,7 +1936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1951,7 +1956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1968,7 +1973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1985,7 +1990,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2002,7 +2007,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2019,7 +2024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2036,7 +2041,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2053,7 +2058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2070,7 +2075,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2087,7 +2092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2104,7 +2109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2121,7 +2126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2138,7 +2143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2155,7 +2160,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2172,7 +2177,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2189,7 +2194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2206,7 +2211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2223,7 +2228,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2240,7 +2245,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2254,7 +2259,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2271,7 +2276,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2288,7 +2293,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2305,7 +2310,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2322,7 +2327,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2339,7 +2344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2356,7 +2361,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2373,7 +2378,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2390,7 +2395,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2407,7 +2412,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2434,12 +2439,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="36.21875" customWidth="1"/>
+    <col min="2" max="2" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -2450,7 +2455,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>120</v>
       </c>
@@ -2461,7 +2466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>122</v>
       </c>
@@ -2472,7 +2477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>124</v>
       </c>
@@ -2483,7 +2488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -2494,7 +2499,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -2505,7 +2510,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -2516,132 +2521,132 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>158</v>
       </c>
@@ -2655,9 +2660,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H327"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -2683,7 +2688,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>165</v>
       </c>
@@ -2703,7 +2708,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>169</v>
       </c>
@@ -2729,7 +2734,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>172</v>
       </c>
@@ -2755,7 +2760,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>178</v>
       </c>
@@ -2763,7 +2768,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>182</v>
       </c>
@@ -2771,7 +2776,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>183</v>
       </c>
@@ -2779,7 +2784,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>184</v>
       </c>
@@ -2787,7 +2792,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>185</v>
       </c>
@@ -2795,7 +2800,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>186</v>
       </c>
@@ -2803,7 +2808,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>187</v>
       </c>
@@ -2811,7 +2816,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>188</v>
       </c>
@@ -2819,7 +2824,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>189</v>
       </c>
@@ -2827,7 +2832,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>190</v>
       </c>
@@ -2835,7 +2840,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>191</v>
       </c>
@@ -2843,7 +2848,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>192</v>
       </c>
@@ -2851,7 +2856,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>193</v>
       </c>
@@ -2859,7 +2864,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>194</v>
       </c>
@@ -2867,7 +2872,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>195</v>
       </c>
@@ -2875,7 +2880,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>196</v>
       </c>
@@ -2883,7 +2888,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -2891,7 +2896,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>198</v>
       </c>
@@ -2899,7 +2904,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>199</v>
       </c>
@@ -2907,7 +2912,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>200</v>
       </c>
@@ -2915,7 +2920,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>201</v>
       </c>
@@ -2923,7 +2928,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>202</v>
       </c>
@@ -2931,7 +2936,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>203</v>
       </c>
@@ -2939,7 +2944,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>204</v>
       </c>
@@ -2947,7 +2952,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>205</v>
       </c>
@@ -2955,7 +2960,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>206</v>
       </c>
@@ -2963,7 +2968,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>207</v>
       </c>
@@ -2971,7 +2976,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>208</v>
       </c>
@@ -2979,7 +2984,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>209</v>
       </c>
@@ -2987,7 +2992,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>210</v>
       </c>
@@ -2995,7 +3000,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>211</v>
       </c>
@@ -3003,7 +3008,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>212</v>
       </c>
@@ -3011,7 +3016,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>213</v>
       </c>
@@ -3019,7 +3024,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>214</v>
       </c>
@@ -3027,7 +3032,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>215</v>
       </c>
@@ -3035,7 +3040,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>216</v>
       </c>
@@ -3043,7 +3048,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>217</v>
       </c>
@@ -3051,7 +3056,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>218</v>
       </c>
@@ -3059,7 +3064,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>219</v>
       </c>
@@ -3067,7 +3072,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>220</v>
       </c>
@@ -3075,7 +3080,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>221</v>
       </c>
@@ -3083,7 +3088,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>222</v>
       </c>
@@ -3091,7 +3096,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>223</v>
       </c>
@@ -3099,7 +3104,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>224</v>
       </c>
@@ -3107,7 +3112,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>225</v>
       </c>
@@ -3115,7 +3120,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>226</v>
       </c>
@@ -3123,7 +3128,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>227</v>
       </c>
@@ -3131,7 +3136,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>228</v>
       </c>
@@ -3139,7 +3144,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>229</v>
       </c>
@@ -3147,7 +3152,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>230</v>
       </c>
@@ -3155,7 +3160,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>231</v>
       </c>
@@ -3163,7 +3168,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>232</v>
       </c>
@@ -3171,7 +3176,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>233</v>
       </c>
@@ -3179,7 +3184,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>234</v>
       </c>
@@ -3187,7 +3192,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -3195,7 +3200,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>236</v>
       </c>
@@ -3203,7 +3208,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>237</v>
       </c>
@@ -3211,7 +3216,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>238</v>
       </c>
@@ -3219,7 +3224,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>239</v>
       </c>
@@ -3227,7 +3232,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>241</v>
       </c>
@@ -3235,7 +3240,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>242</v>
       </c>
@@ -3243,7 +3248,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>243</v>
       </c>
@@ -3251,7 +3256,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>244</v>
       </c>
@@ -3259,7 +3264,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>245</v>
       </c>
@@ -3267,7 +3272,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>246</v>
       </c>
@@ -3275,7 +3280,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>247</v>
       </c>
@@ -3283,7 +3288,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>248</v>
       </c>
@@ -3291,7 +3296,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>249</v>
       </c>
@@ -3299,7 +3304,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>250</v>
       </c>
@@ -3307,7 +3312,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>251</v>
       </c>
@@ -3315,7 +3320,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>252</v>
       </c>
@@ -3323,7 +3328,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>253</v>
       </c>
@@ -3331,7 +3336,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>254</v>
       </c>
@@ -3339,7 +3344,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>255</v>
       </c>
@@ -3347,7 +3352,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>256</v>
       </c>
@@ -3355,7 +3360,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>257</v>
       </c>
@@ -3363,7 +3368,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>258</v>
       </c>
@@ -3371,7 +3376,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>259</v>
       </c>
@@ -3379,7 +3384,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>260</v>
       </c>
@@ -3387,7 +3392,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>261</v>
       </c>
@@ -3395,7 +3400,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>262</v>
       </c>
@@ -3403,7 +3408,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>263</v>
       </c>
@@ -3411,7 +3416,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>264</v>
       </c>
@@ -3419,7 +3424,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>265</v>
       </c>
@@ -3427,7 +3432,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>266</v>
       </c>
@@ -3435,7 +3440,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>267</v>
       </c>
@@ -3443,7 +3448,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>268</v>
       </c>
@@ -3451,7 +3456,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>269</v>
       </c>
@@ -3459,7 +3464,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>270</v>
       </c>
@@ -3467,7 +3472,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>271</v>
       </c>
@@ -3475,7 +3480,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>272</v>
       </c>
@@ -3483,7 +3488,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>273</v>
       </c>
@@ -3491,7 +3496,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>274</v>
       </c>
@@ -3499,7 +3504,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>275</v>
       </c>
@@ -3507,7 +3512,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>276</v>
       </c>
@@ -3515,7 +3520,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>277</v>
       </c>
@@ -3523,7 +3528,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>278</v>
       </c>
@@ -3531,7 +3536,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>279</v>
       </c>
@@ -3539,7 +3544,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>280</v>
       </c>
@@ -3547,7 +3552,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>281</v>
       </c>
@@ -3555,7 +3560,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>282</v>
       </c>
@@ -3563,7 +3568,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>283</v>
       </c>
@@ -3571,7 +3576,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>284</v>
       </c>
@@ -3579,7 +3584,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>285</v>
       </c>
@@ -3587,7 +3592,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>286</v>
       </c>
@@ -3595,7 +3600,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>287</v>
       </c>
@@ -3603,7 +3608,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>288</v>
       </c>
@@ -3611,7 +3616,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>289</v>
       </c>
@@ -3619,7 +3624,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>290</v>
       </c>
@@ -3627,7 +3632,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>291</v>
       </c>
@@ -3635,7 +3640,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>292</v>
       </c>
@@ -3643,7 +3648,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>293</v>
       </c>
@@ -3651,7 +3656,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>294</v>
       </c>
@@ -3659,7 +3664,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>295</v>
       </c>
@@ -3667,7 +3672,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>296</v>
       </c>
@@ -3675,7 +3680,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>297</v>
       </c>
@@ -3683,7 +3688,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>298</v>
       </c>
@@ -3691,7 +3696,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>299</v>
       </c>
@@ -3699,7 +3704,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>300</v>
       </c>
@@ -3707,7 +3712,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>301</v>
       </c>
@@ -3715,7 +3720,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>302</v>
       </c>
@@ -3723,7 +3728,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>303</v>
       </c>
@@ -3731,7 +3736,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>304</v>
       </c>
@@ -3739,7 +3744,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>305</v>
       </c>
@@ -3747,7 +3752,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>306</v>
       </c>
@@ -3755,7 +3760,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>307</v>
       </c>
@@ -3763,7 +3768,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>308</v>
       </c>
@@ -3771,7 +3776,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>309</v>
       </c>
@@ -3779,7 +3784,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>310</v>
       </c>
@@ -3787,7 +3792,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>311</v>
       </c>
@@ -3795,7 +3800,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>312</v>
       </c>
@@ -3803,7 +3808,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>313</v>
       </c>
@@ -3811,7 +3816,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>314</v>
       </c>
@@ -3819,7 +3824,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>315</v>
       </c>
@@ -3827,7 +3832,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>316</v>
       </c>
@@ -3835,7 +3840,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>317</v>
       </c>
@@ -3843,7 +3848,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>318</v>
       </c>
@@ -3851,7 +3856,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>319</v>
       </c>
@@ -3859,7 +3864,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>320</v>
       </c>
@@ -3867,7 +3872,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>321</v>
       </c>
@@ -3875,7 +3880,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>322</v>
       </c>
@@ -3883,7 +3888,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>323</v>
       </c>
@@ -3891,7 +3896,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>324</v>
       </c>
@@ -3899,7 +3904,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>325</v>
       </c>
@@ -3907,7 +3912,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>326</v>
       </c>
@@ -3915,7 +3920,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>327</v>
       </c>
@@ -3923,7 +3928,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>328</v>
       </c>
@@ -3931,7 +3936,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>329</v>
       </c>
@@ -3939,7 +3944,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>330</v>
       </c>
@@ -3947,7 +3952,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>331</v>
       </c>
@@ -3955,7 +3960,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>332</v>
       </c>
@@ -3963,7 +3968,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>333</v>
       </c>
@@ -3971,7 +3976,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>334</v>
       </c>
@@ -3979,7 +3984,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>335</v>
       </c>
@@ -3987,7 +3992,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>336</v>
       </c>
@@ -3995,7 +4000,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>337</v>
       </c>
@@ -4003,7 +4008,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>338</v>
       </c>
@@ -4011,7 +4016,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>339</v>
       </c>
@@ -4019,7 +4024,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>340</v>
       </c>
@@ -4027,822 +4032,822 @@
         <v>340</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E164" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E165" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E166" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E167" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E168" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E169" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E170" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E171" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E172" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E173" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E174" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E175" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E176" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E177" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E178" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E179" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E180" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E181" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E182" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E183" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E184" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E185" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E186" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E187" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E188" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E189" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E190" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E191" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E192" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E193" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E194" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E195" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="196" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E196" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="197" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E197" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E198" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="199" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E199" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="200" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E200" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="201" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E201" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="202" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E202" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="203" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E203" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="204" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E204" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="205" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E205" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="206" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E206" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="207" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E207" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="208" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E208" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E209" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E210" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E211" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E212" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E213" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E214" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E215" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E216" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E217" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E218" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E219" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E220" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E221" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E222" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E223" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E224" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E225" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E226" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E227" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E228" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E229" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E230" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E231" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E232" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E233" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E234" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E235" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E236" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E237" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E238" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E239" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E240" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E241" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E242" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E243" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E244" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E245" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E246" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E247" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E248" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E249" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E250" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E251" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E252" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E253" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E254" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E255" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E256" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E257" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E258" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E259" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E260" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E261" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E262" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E263" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E264" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E265" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E266" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E267" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E268" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E269" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E270" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E271" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E272" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E273" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E274" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E275" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E276" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E277" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E278" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E279" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="280" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E280" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="281" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E281" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="282" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E282" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="283" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E283" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="284" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E284" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="285" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E285" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="286" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E286" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="287" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E287" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="288" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E288" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="289" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E289" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="290" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E290" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="291" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E291" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="292" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E292" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="293" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E293" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="294" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E294" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="295" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E295" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="296" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E296" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="297" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E297" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="298" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E298" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="299" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E299" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="300" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E300" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="301" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E301" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="302" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E302" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="303" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E303" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="304" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E304" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="305" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E305" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="306" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E306" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="307" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E307" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="308" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E308" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="309" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E309" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="310" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E310" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="311" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E311" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="312" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E312" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="313" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E313" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="314" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E314" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="315" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E315" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="316" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E316" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="317" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E317" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="318" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E318" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="319" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E319" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="320" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E320" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="321" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E321" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="322" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E322" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="323" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E323" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="324" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E324" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="325" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E325" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="326" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E326" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="327" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E327" t="s">
         <v>504</v>
       </c>
@@ -4856,23 +4861,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.9140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.75" style="2" customWidth="1"/>
     <col min="6" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="9" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.21875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.75" style="2" customWidth="1"/>
     <col min="13" max="14" width="9" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4892,7 +4897,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -4903,7 +4908,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4914,7 +4919,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4922,7 +4927,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4939,7 +4944,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4956,7 +4961,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -4967,7 +4972,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -4978,7 +4983,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -4989,7 +4994,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -4997,7 +5002,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -5014,7 +5019,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -5025,7 +5030,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -5036,7 +5041,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -5047,7 +5052,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -5058,7 +5063,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -5066,7 +5071,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -5083,7 +5088,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -5097,7 +5102,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -5111,7 +5116,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -5125,7 +5130,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -5139,7 +5144,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -5153,7 +5158,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -5167,7 +5172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -5181,7 +5186,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -5189,7 +5194,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -5197,7 +5202,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -5208,7 +5213,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -5216,7 +5221,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -5230,7 +5235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -5238,7 +5243,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -5249,7 +5254,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -5260,7 +5265,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -5268,7 +5273,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -5276,7 +5281,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -5284,7 +5289,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -5292,7 +5297,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -5300,7 +5305,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -5308,7 +5313,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -5319,7 +5324,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -5327,7 +5332,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -5335,7 +5340,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -5343,7 +5348,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -5354,7 +5359,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -5365,7 +5370,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -5376,7 +5381,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -5384,7 +5389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -5395,7 +5400,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -5406,7 +5411,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -5417,7 +5422,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -5425,7 +5430,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -5433,7 +5438,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -5441,7 +5446,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -5458,7 +5463,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -5475,7 +5480,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -5492,7 +5497,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5509,7 +5514,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -5520,7 +5525,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -5531,22 +5536,22 @@
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -5554,15 +5559,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5573,7 +5579,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5584,7 +5590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5595,7 +5601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5606,7 +5612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5617,7 +5623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5628,7 +5634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5639,7 +5645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5650,7 +5656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5670,15 +5676,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="45.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.4140625" style="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="55.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5686,7 +5692,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5694,7 +5700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -5702,7 +5708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -5710,7 +5716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -5718,7 +5724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -5726,7 +5732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5734,7 +5740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5742,7 +5748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5750,7 +5756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5758,7 +5764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5766,7 +5772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5774,7 +5780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5782,7 +5788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5790,7 +5796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5798,7 +5804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5806,7 +5812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5814,7 +5820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5822,7 +5828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5830,7 +5836,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5838,7 +5844,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5846,7 +5852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5854,7 +5860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5862,7 +5868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5870,7 +5876,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5878,7 +5884,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5886,7 +5892,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5894,7 +5900,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5902,7 +5908,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5910,7 +5916,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5927,20 +5933,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.08203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="26.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.9140625" style="1" customWidth="1"/>
     <col min="8" max="9" width="9" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="96.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
@@ -5960,7 +5966,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5972,7 +5978,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -5992,12 +5998,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6005,7 +6011,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6013,7 +6019,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6030,17 +6036,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="9" style="3" customWidth="1"/>
     <col min="6" max="6" width="15" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.4140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="3" customWidth="1"/>
     <col min="9" max="10" width="9" style="3" customWidth="1"/>
     <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6066,7 +6072,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -6089,9 +6095,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6114,7 +6120,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6128,9 +6134,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>99</v>
       </c>
@@ -6153,7 +6159,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>

--- a/Assets/Documents/全局配置表.xlsx
+++ b/Assets/Documents/全局配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\何睿豪\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F47A7F-8AFD-4855-A2B5-261360B46A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F92C524-EA5A-492C-8BDC-1D0C024ADF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="素材库" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="569">
   <si>
     <t>ID</t>
   </si>
@@ -206,1423 +206,1625 @@
     <t>None Heal1</t>
   </si>
   <si>
+    <t>None Attack0</t>
+  </si>
+  <si>
+    <t>None Heal-2</t>
+  </si>
+  <si>
+    <t>None Heal-1</t>
+  </si>
+  <si>
+    <t>None Heal-5</t>
+  </si>
+  <si>
+    <t>Less11 Defence2</t>
+  </si>
+  <si>
+    <t>Less6 Attack5</t>
+  </si>
+  <si>
+    <t>Equal3 Defence8</t>
+  </si>
+  <si>
+    <t>Equal6 Defence8</t>
+  </si>
+  <si>
+    <t>Equal1 Attack13</t>
+  </si>
+  <si>
+    <t>Equal4 Attack13</t>
+  </si>
+  <si>
+    <t>Equal7 Attack13 | Equal10 Attack13</t>
+  </si>
+  <si>
+    <t>Less10 Defence4</t>
+  </si>
+  <si>
+    <t>意图列表</t>
+  </si>
+  <si>
+    <t>霉豆腐</t>
+  </si>
+  <si>
+    <t>榴莲汁</t>
+  </si>
+  <si>
+    <t>苦瓜精</t>
+  </si>
+  <si>
+    <t>小块盐</t>
+  </si>
+  <si>
+    <t>小瓶生抽</t>
+  </si>
+  <si>
+    <t>味精</t>
+  </si>
+  <si>
+    <t>胡椒水</t>
+  </si>
+  <si>
+    <t>大碗胡椒水</t>
+  </si>
+  <si>
+    <t>注释：玩家从任何途径获取到素材的时候，从素材库中随机选取一个之前没用抽取过的id对应的素材，因为有些素材可能是只有怪物才有的，所以要做好分离</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>升级后的素材意图列表索引</t>
+  </si>
+  <si>
+    <t>注释：和素材库一样，这里存的是游戏中所有遗物的定义。如果某个遗物是专门作为怪物遗物，因为他在游戏中不可能被合成成卡牌，因此素材意图置空即可</t>
+  </si>
+  <si>
+    <t>精猪后腿肉</t>
+  </si>
+  <si>
+    <t>注释：同玩家素材池</t>
+  </si>
+  <si>
+    <t>卡牌1</t>
+  </si>
+  <si>
+    <t>卡牌2</t>
+  </si>
+  <si>
+    <t>卡牌3</t>
+  </si>
+  <si>
+    <t>卡牌4</t>
+  </si>
+  <si>
+    <t>遗物列表</t>
+  </si>
+  <si>
+    <t>注释：卡牌列填写的数字，代表着组成他们的素材id。遗物列表下填写的数字，代表小怪会携带的所有遗物。两个数字之间用空格分开</t>
+  </si>
+  <si>
+    <t>同样的，当进入小怪战斗后，会抽取一个之前没抽到过的卡牌组</t>
+  </si>
+  <si>
+    <t>1 2 3</t>
+  </si>
+  <si>
+    <t>2 3</t>
+  </si>
+  <si>
+    <t>注释：同小怪池</t>
+  </si>
+  <si>
+    <t>同小怪池</t>
+  </si>
+  <si>
+    <t>索引ID</t>
+  </si>
+  <si>
+    <t>合成表</t>
+  </si>
+  <si>
+    <t>合成物</t>
+  </si>
+  <si>
+    <t>N2.1</t>
+  </si>
+  <si>
+    <t>香菇*1</t>
+  </si>
+  <si>
+    <t>n2.2</t>
+  </si>
+  <si>
+    <t>任意肉*1</t>
+  </si>
+  <si>
+    <t>N2.3</t>
+  </si>
+  <si>
+    <t>糊的肉*1</t>
+  </si>
+  <si>
+    <t>N2.4</t>
+  </si>
+  <si>
+    <t>任意水*1+盐*1</t>
+  </si>
+  <si>
+    <t>盐水</t>
+  </si>
+  <si>
+    <t>N2.5</t>
+  </si>
+  <si>
+    <t>盐水*1+任意水*1</t>
+  </si>
+  <si>
+    <t>N2.6</t>
+  </si>
+  <si>
+    <t>任意2稀有度及以上的水*1+盐*1</t>
+  </si>
+  <si>
+    <t>N2.7</t>
+  </si>
+  <si>
+    <t>N2.8</t>
+  </si>
+  <si>
+    <t>N2.9</t>
+  </si>
+  <si>
+    <t>N2.10</t>
+  </si>
+  <si>
+    <t>N2.11</t>
+  </si>
+  <si>
+    <t>N2.12</t>
+  </si>
+  <si>
+    <t>N2.13</t>
+  </si>
+  <si>
+    <t>N2.14</t>
+  </si>
+  <si>
+    <t>N2.15</t>
+  </si>
+  <si>
+    <t>N2.16</t>
+  </si>
+  <si>
+    <t>N2.17</t>
+  </si>
+  <si>
+    <t>N2.18</t>
+  </si>
+  <si>
+    <t>N2.19</t>
+  </si>
+  <si>
+    <t>N2.20</t>
+  </si>
+  <si>
+    <t>N2.21</t>
+  </si>
+  <si>
+    <t>N2.22</t>
+  </si>
+  <si>
+    <t>N2.23</t>
+  </si>
+  <si>
+    <t>N2.24</t>
+  </si>
+  <si>
+    <t>N2.25</t>
+  </si>
+  <si>
+    <t>N2.26</t>
+  </si>
+  <si>
+    <t>N2.27</t>
+  </si>
+  <si>
+    <t>N2.28</t>
+  </si>
+  <si>
+    <t>N2.29</t>
+  </si>
+  <si>
+    <t>N2.30</t>
+  </si>
+  <si>
+    <t>N2.31</t>
+  </si>
+  <si>
+    <t>N2.32</t>
+  </si>
+  <si>
+    <t>角色名字</t>
+  </si>
+  <si>
+    <t>升级所需经验</t>
+  </si>
+  <si>
+    <t>角色星级</t>
+  </si>
+  <si>
+    <t>背包里显示的图标</t>
+  </si>
+  <si>
+    <t>升级路径</t>
+  </si>
+  <si>
+    <t>特殊机制与加成</t>
+  </si>
+  <si>
+    <t>N1.0</t>
+  </si>
+  <si>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;2-&gt;3-&gt;3</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>N1.1</t>
+  </si>
+  <si>
+    <t>无-&gt;无&gt;无-&gt;无</t>
+  </si>
+  <si>
+    <t>猪腿煲汤</t>
+  </si>
+  <si>
+    <t>N1.2</t>
+  </si>
+  <si>
+    <t>无-&gt;hp+3-&gt;无-&gt;无</t>
+  </si>
+  <si>
+    <t>战斗开始获得十格挡</t>
+  </si>
+  <si>
+    <t>特级精品猪油+精品猪后腿肉+咸水</t>
+  </si>
+  <si>
+    <t>N1.3</t>
+  </si>
+  <si>
+    <t>海藻水+海藻气泡+海藻团块</t>
+  </si>
+  <si>
+    <t>N1.4</t>
+  </si>
+  <si>
+    <t>N1.5</t>
+  </si>
+  <si>
+    <t>N1.6</t>
+  </si>
+  <si>
+    <t>N1.7</t>
+  </si>
+  <si>
+    <t>N1.8</t>
+  </si>
+  <si>
+    <t>N1.9</t>
+  </si>
+  <si>
+    <t>N1.10</t>
+  </si>
+  <si>
+    <t>N1.11</t>
+  </si>
+  <si>
+    <t>N1.12</t>
+  </si>
+  <si>
+    <t>N1.13</t>
+  </si>
+  <si>
+    <t>N1.14</t>
+  </si>
+  <si>
+    <t>N1.15</t>
+  </si>
+  <si>
+    <t>N1.16</t>
+  </si>
+  <si>
+    <t>N1.17</t>
+  </si>
+  <si>
+    <t>N1.18</t>
+  </si>
+  <si>
+    <t>N1.19</t>
+  </si>
+  <si>
+    <t>N1.20</t>
+  </si>
+  <si>
+    <t>N1.21</t>
+  </si>
+  <si>
+    <t>N1.22</t>
+  </si>
+  <si>
+    <t>N1.23</t>
+  </si>
+  <si>
+    <t>N1.24</t>
+  </si>
+  <si>
+    <t>N1.25</t>
+  </si>
+  <si>
+    <t>N1.26</t>
+  </si>
+  <si>
+    <t>N1.27</t>
+  </si>
+  <si>
+    <t>N1.28</t>
+  </si>
+  <si>
+    <t>N1.29</t>
+  </si>
+  <si>
+    <t>N1.30</t>
+  </si>
+  <si>
+    <t>N1.31</t>
+  </si>
+  <si>
+    <t>N1.32</t>
+  </si>
+  <si>
+    <t>N1.33</t>
+  </si>
+  <si>
+    <t>N1.34</t>
+  </si>
+  <si>
+    <t>N1.35</t>
+  </si>
+  <si>
+    <t>N1.36</t>
+  </si>
+  <si>
+    <t>N1.37</t>
+  </si>
+  <si>
+    <t>N1.38</t>
+  </si>
+  <si>
+    <t>N1.39</t>
+  </si>
+  <si>
+    <t>N1.40</t>
+  </si>
+  <si>
+    <t>N1.41</t>
+  </si>
+  <si>
+    <t>N1.42</t>
+  </si>
+  <si>
+    <t>N1.43</t>
+  </si>
+  <si>
+    <t>N1.44</t>
+  </si>
+  <si>
+    <t>N1.45</t>
+  </si>
+  <si>
+    <t>N1.46</t>
+  </si>
+  <si>
+    <t>N1.47</t>
+  </si>
+  <si>
+    <t>N1.48</t>
+  </si>
+  <si>
+    <t>N1.49</t>
+  </si>
+  <si>
+    <t>N1.50</t>
+  </si>
+  <si>
+    <t>N1.51</t>
+  </si>
+  <si>
+    <t>N1.52</t>
+  </si>
+  <si>
+    <t>N1.53</t>
+  </si>
+  <si>
+    <t>N1.54</t>
+  </si>
+  <si>
+    <t>N1.55</t>
+  </si>
+  <si>
+    <t>N1.56</t>
+  </si>
+  <si>
+    <t>N1.57</t>
+  </si>
+  <si>
+    <t>N1.58</t>
+  </si>
+  <si>
+    <t>N1.59</t>
+  </si>
+  <si>
+    <t>N1.60</t>
+  </si>
+  <si>
+    <t>N1.61</t>
+  </si>
+  <si>
+    <t>N1.62</t>
+  </si>
+  <si>
+    <t>N1.63</t>
+  </si>
+  <si>
+    <t>N1.64</t>
+  </si>
+  <si>
+    <t>N1.65</t>
+  </si>
+  <si>
+    <t>N1.66</t>
+  </si>
+  <si>
+    <t>N1.67</t>
+  </si>
+  <si>
+    <t>N1.68</t>
+  </si>
+  <si>
+    <t>N1.69</t>
+  </si>
+  <si>
+    <t>N1.70</t>
+  </si>
+  <si>
+    <t>N1.71</t>
+  </si>
+  <si>
+    <t>N1.72</t>
+  </si>
+  <si>
+    <t>N1.73</t>
+  </si>
+  <si>
+    <t>N1.74</t>
+  </si>
+  <si>
+    <t>N1.75</t>
+  </si>
+  <si>
+    <t>N1.76</t>
+  </si>
+  <si>
+    <t>N1.77</t>
+  </si>
+  <si>
+    <t>N1.78</t>
+  </si>
+  <si>
+    <t>N1.79</t>
+  </si>
+  <si>
+    <t>N1.80</t>
+  </si>
+  <si>
+    <t>N1.81</t>
+  </si>
+  <si>
+    <t>N1.82</t>
+  </si>
+  <si>
+    <t>N1.83</t>
+  </si>
+  <si>
+    <t>N1.84</t>
+  </si>
+  <si>
+    <t>N1.85</t>
+  </si>
+  <si>
+    <t>N1.86</t>
+  </si>
+  <si>
+    <t>N1.87</t>
+  </si>
+  <si>
+    <t>N1.88</t>
+  </si>
+  <si>
+    <t>N1.89</t>
+  </si>
+  <si>
+    <t>N1.90</t>
+  </si>
+  <si>
+    <t>N1.91</t>
+  </si>
+  <si>
+    <t>N1.92</t>
+  </si>
+  <si>
+    <t>N1.93</t>
+  </si>
+  <si>
+    <t>N1.94</t>
+  </si>
+  <si>
+    <t>N1.95</t>
+  </si>
+  <si>
+    <t>N1.96</t>
+  </si>
+  <si>
+    <t>N1.97</t>
+  </si>
+  <si>
+    <t>N1.98</t>
+  </si>
+  <si>
+    <t>N1.99</t>
+  </si>
+  <si>
+    <t>N1.100</t>
+  </si>
+  <si>
+    <t>N1.101</t>
+  </si>
+  <si>
+    <t>N1.102</t>
+  </si>
+  <si>
+    <t>N1.103</t>
+  </si>
+  <si>
+    <t>N1.104</t>
+  </si>
+  <si>
+    <t>N1.105</t>
+  </si>
+  <si>
+    <t>N1.106</t>
+  </si>
+  <si>
+    <t>N1.107</t>
+  </si>
+  <si>
+    <t>N1.108</t>
+  </si>
+  <si>
+    <t>N1.109</t>
+  </si>
+  <si>
+    <t>N1.110</t>
+  </si>
+  <si>
+    <t>N1.111</t>
+  </si>
+  <si>
+    <t>N1.112</t>
+  </si>
+  <si>
+    <t>N1.113</t>
+  </si>
+  <si>
+    <t>N1.114</t>
+  </si>
+  <si>
+    <t>N1.115</t>
+  </si>
+  <si>
+    <t>N1.116</t>
+  </si>
+  <si>
+    <t>N1.117</t>
+  </si>
+  <si>
+    <t>N1.118</t>
+  </si>
+  <si>
+    <t>N1.119</t>
+  </si>
+  <si>
+    <t>N1.120</t>
+  </si>
+  <si>
+    <t>N1.121</t>
+  </si>
+  <si>
+    <t>N1.122</t>
+  </si>
+  <si>
+    <t>N1.123</t>
+  </si>
+  <si>
+    <t>N1.124</t>
+  </si>
+  <si>
+    <t>N1.125</t>
+  </si>
+  <si>
+    <t>N1.126</t>
+  </si>
+  <si>
+    <t>N1.127</t>
+  </si>
+  <si>
+    <t>N1.128</t>
+  </si>
+  <si>
+    <t>N1.129</t>
+  </si>
+  <si>
+    <t>N1.130</t>
+  </si>
+  <si>
+    <t>N1.131</t>
+  </si>
+  <si>
+    <t>N1.132</t>
+  </si>
+  <si>
+    <t>N1.133</t>
+  </si>
+  <si>
+    <t>N1.134</t>
+  </si>
+  <si>
+    <t>N1.135</t>
+  </si>
+  <si>
+    <t>N1.136</t>
+  </si>
+  <si>
+    <t>N1.137</t>
+  </si>
+  <si>
+    <t>N1.138</t>
+  </si>
+  <si>
+    <t>N1.139</t>
+  </si>
+  <si>
+    <t>N1.140</t>
+  </si>
+  <si>
+    <t>N1.141</t>
+  </si>
+  <si>
+    <t>N1.142</t>
+  </si>
+  <si>
+    <t>N1.143</t>
+  </si>
+  <si>
+    <t>N1.144</t>
+  </si>
+  <si>
+    <t>N1.145</t>
+  </si>
+  <si>
+    <t>N1.146</t>
+  </si>
+  <si>
+    <t>N1.147</t>
+  </si>
+  <si>
+    <t>N1.148</t>
+  </si>
+  <si>
+    <t>N1.149</t>
+  </si>
+  <si>
+    <t>N1.150</t>
+  </si>
+  <si>
+    <t>N1.151</t>
+  </si>
+  <si>
+    <t>N1.152</t>
+  </si>
+  <si>
+    <t>N1.153</t>
+  </si>
+  <si>
+    <t>N1.154</t>
+  </si>
+  <si>
+    <t>N1.155</t>
+  </si>
+  <si>
+    <t>N1.156</t>
+  </si>
+  <si>
+    <t>N1.157</t>
+  </si>
+  <si>
+    <t>N1.158</t>
+  </si>
+  <si>
+    <t>N1.159</t>
+  </si>
+  <si>
+    <t>N1.160</t>
+  </si>
+  <si>
+    <t>N1.161</t>
+  </si>
+  <si>
+    <t>N1.162</t>
+  </si>
+  <si>
+    <t>N1.163</t>
+  </si>
+  <si>
+    <t>N1.164</t>
+  </si>
+  <si>
+    <t>N1.165</t>
+  </si>
+  <si>
+    <t>N1.166</t>
+  </si>
+  <si>
+    <t>N1.167</t>
+  </si>
+  <si>
+    <t>N1.168</t>
+  </si>
+  <si>
+    <t>N1.169</t>
+  </si>
+  <si>
+    <t>N1.170</t>
+  </si>
+  <si>
+    <t>N1.171</t>
+  </si>
+  <si>
+    <t>N1.172</t>
+  </si>
+  <si>
+    <t>N1.173</t>
+  </si>
+  <si>
+    <t>N1.174</t>
+  </si>
+  <si>
+    <t>N1.175</t>
+  </si>
+  <si>
+    <t>N1.176</t>
+  </si>
+  <si>
+    <t>N1.177</t>
+  </si>
+  <si>
+    <t>N1.178</t>
+  </si>
+  <si>
+    <t>N1.179</t>
+  </si>
+  <si>
+    <t>N1.180</t>
+  </si>
+  <si>
+    <t>N1.181</t>
+  </si>
+  <si>
+    <t>N1.182</t>
+  </si>
+  <si>
+    <t>N1.183</t>
+  </si>
+  <si>
+    <t>N1.184</t>
+  </si>
+  <si>
+    <t>N1.185</t>
+  </si>
+  <si>
+    <t>N1.186</t>
+  </si>
+  <si>
+    <t>N1.187</t>
+  </si>
+  <si>
+    <t>N1.188</t>
+  </si>
+  <si>
+    <t>N1.189</t>
+  </si>
+  <si>
+    <t>N1.190</t>
+  </si>
+  <si>
+    <t>N1.191</t>
+  </si>
+  <si>
+    <t>N1.192</t>
+  </si>
+  <si>
+    <t>N1.193</t>
+  </si>
+  <si>
+    <t>N1.194</t>
+  </si>
+  <si>
+    <t>N1.195</t>
+  </si>
+  <si>
+    <t>N1.196</t>
+  </si>
+  <si>
+    <t>N1.197</t>
+  </si>
+  <si>
+    <t>N1.198</t>
+  </si>
+  <si>
+    <t>N1.199</t>
+  </si>
+  <si>
+    <t>N1.200</t>
+  </si>
+  <si>
+    <t>N1.201</t>
+  </si>
+  <si>
+    <t>N1.202</t>
+  </si>
+  <si>
+    <t>N1.203</t>
+  </si>
+  <si>
+    <t>N1.204</t>
+  </si>
+  <si>
+    <t>N1.205</t>
+  </si>
+  <si>
+    <t>N1.206</t>
+  </si>
+  <si>
+    <t>N1.207</t>
+  </si>
+  <si>
+    <t>N1.208</t>
+  </si>
+  <si>
+    <t>N1.209</t>
+  </si>
+  <si>
+    <t>N1.210</t>
+  </si>
+  <si>
+    <t>N1.211</t>
+  </si>
+  <si>
+    <t>N1.212</t>
+  </si>
+  <si>
+    <t>N1.213</t>
+  </si>
+  <si>
+    <t>N1.214</t>
+  </si>
+  <si>
+    <t>N1.215</t>
+  </si>
+  <si>
+    <t>N1.216</t>
+  </si>
+  <si>
+    <t>N1.217</t>
+  </si>
+  <si>
+    <t>N1.218</t>
+  </si>
+  <si>
+    <t>N1.219</t>
+  </si>
+  <si>
+    <t>N1.220</t>
+  </si>
+  <si>
+    <t>N1.221</t>
+  </si>
+  <si>
+    <t>N1.222</t>
+  </si>
+  <si>
+    <t>N1.223</t>
+  </si>
+  <si>
+    <t>N1.224</t>
+  </si>
+  <si>
+    <t>N1.225</t>
+  </si>
+  <si>
+    <t>N1.226</t>
+  </si>
+  <si>
+    <t>N1.227</t>
+  </si>
+  <si>
+    <t>N1.228</t>
+  </si>
+  <si>
+    <t>N1.229</t>
+  </si>
+  <si>
+    <t>N1.230</t>
+  </si>
+  <si>
+    <t>N1.231</t>
+  </si>
+  <si>
+    <t>N1.232</t>
+  </si>
+  <si>
+    <t>N1.233</t>
+  </si>
+  <si>
+    <t>N1.234</t>
+  </si>
+  <si>
+    <t>N1.235</t>
+  </si>
+  <si>
+    <t>N1.236</t>
+  </si>
+  <si>
+    <t>N1.237</t>
+  </si>
+  <si>
+    <t>N1.238</t>
+  </si>
+  <si>
+    <t>N1.239</t>
+  </si>
+  <si>
+    <t>N1.240</t>
+  </si>
+  <si>
+    <t>N1.241</t>
+  </si>
+  <si>
+    <t>N1.242</t>
+  </si>
+  <si>
+    <t>N1.243</t>
+  </si>
+  <si>
+    <t>N1.244</t>
+  </si>
+  <si>
+    <t>N1.245</t>
+  </si>
+  <si>
+    <t>N1.246</t>
+  </si>
+  <si>
+    <t>N1.247</t>
+  </si>
+  <si>
+    <t>N1.248</t>
+  </si>
+  <si>
+    <t>N1.249</t>
+  </si>
+  <si>
+    <t>N1.250</t>
+  </si>
+  <si>
+    <t>N1.251</t>
+  </si>
+  <si>
+    <t>N1.252</t>
+  </si>
+  <si>
+    <t>N1.253</t>
+  </si>
+  <si>
+    <t>N1.254</t>
+  </si>
+  <si>
+    <t>N1.255</t>
+  </si>
+  <si>
+    <t>N1.256</t>
+  </si>
+  <si>
+    <t>N1.257</t>
+  </si>
+  <si>
+    <t>N1.258</t>
+  </si>
+  <si>
+    <t>N1.259</t>
+  </si>
+  <si>
+    <t>N1.260</t>
+  </si>
+  <si>
+    <t>N1.261</t>
+  </si>
+  <si>
+    <t>N1.262</t>
+  </si>
+  <si>
+    <t>N1.263</t>
+  </si>
+  <si>
+    <t>N1.264</t>
+  </si>
+  <si>
+    <t>N1.265</t>
+  </si>
+  <si>
+    <t>N1.266</t>
+  </si>
+  <si>
+    <t>N1.267</t>
+  </si>
+  <si>
+    <t>N1.268</t>
+  </si>
+  <si>
+    <t>N1.269</t>
+  </si>
+  <si>
+    <t>N1.270</t>
+  </si>
+  <si>
+    <t>N1.271</t>
+  </si>
+  <si>
+    <t>N1.272</t>
+  </si>
+  <si>
+    <t>N1.273</t>
+  </si>
+  <si>
+    <t>N1.274</t>
+  </si>
+  <si>
+    <t>N1.275</t>
+  </si>
+  <si>
+    <t>N1.276</t>
+  </si>
+  <si>
+    <t>N1.277</t>
+  </si>
+  <si>
+    <t>N1.278</t>
+  </si>
+  <si>
+    <t>N1.279</t>
+  </si>
+  <si>
+    <t>N1.280</t>
+  </si>
+  <si>
+    <t>N1.281</t>
+  </si>
+  <si>
+    <t>N1.282</t>
+  </si>
+  <si>
+    <t>N1.283</t>
+  </si>
+  <si>
+    <t>N1.284</t>
+  </si>
+  <si>
+    <t>N1.285</t>
+  </si>
+  <si>
+    <t>N1.286</t>
+  </si>
+  <si>
+    <t>N1.287</t>
+  </si>
+  <si>
+    <t>N1.288</t>
+  </si>
+  <si>
+    <t>N1.289</t>
+  </si>
+  <si>
+    <t>N1.290</t>
+  </si>
+  <si>
+    <t>N1.291</t>
+  </si>
+  <si>
+    <t>N1.292</t>
+  </si>
+  <si>
+    <t>N1.293</t>
+  </si>
+  <si>
+    <t>N1.294</t>
+  </si>
+  <si>
+    <t>N1.295</t>
+  </si>
+  <si>
+    <t>N1.296</t>
+  </si>
+  <si>
+    <t>N1.297</t>
+  </si>
+  <si>
+    <t>N1.298</t>
+  </si>
+  <si>
+    <t>N1.299</t>
+  </si>
+  <si>
+    <t>N1.300</t>
+  </si>
+  <si>
+    <t>N1.301</t>
+  </si>
+  <si>
+    <t>N1.302</t>
+  </si>
+  <si>
+    <t>N1.303</t>
+  </si>
+  <si>
+    <t>N1.304</t>
+  </si>
+  <si>
+    <t>N1.305</t>
+  </si>
+  <si>
+    <t>N1.306</t>
+  </si>
+  <si>
+    <t>N1.307</t>
+  </si>
+  <si>
+    <t>N1.308</t>
+  </si>
+  <si>
+    <t>N1.309</t>
+  </si>
+  <si>
+    <t>N1.310</t>
+  </si>
+  <si>
+    <t>N1.311</t>
+  </si>
+  <si>
+    <t>N1.312</t>
+  </si>
+  <si>
+    <t>N1.313</t>
+  </si>
+  <si>
+    <t>N1.314</t>
+  </si>
+  <si>
+    <t>N1.315</t>
+  </si>
+  <si>
+    <t>N1.316</t>
+  </si>
+  <si>
+    <t>N1.317</t>
+  </si>
+  <si>
+    <t>N1.318</t>
+  </si>
+  <si>
+    <t>N1.319</t>
+  </si>
+  <si>
+    <t>N1.320</t>
+  </si>
+  <si>
+    <t>N1.321</t>
+  </si>
+  <si>
+    <t>N1.322</t>
+  </si>
+  <si>
+    <t>N1.323</t>
+  </si>
+  <si>
+    <t>N1.324</t>
+  </si>
+  <si>
+    <t>N1.325</t>
+  </si>
+  <si>
+    <t>N1.326</t>
+  </si>
+  <si>
+    <t>Greater5 Attack2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less4 Attack2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less4 Attack3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater8 Attack1*2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal6 Attack4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack0*3 | Equal12 Attack0*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack1*3 | Equal12 Attack1*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less6 Attack3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal6 Attack8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater3 Attack2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack1*4 | Equal12 Attack1*4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海洋混混浓汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪腿煲汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less7 Attack5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater5 Attack2*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater0 Attack2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal6 Attack16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack1*4 | Equal12 Attack1*4 | Equal1 Attack1*4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal1 Attack1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Attack3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Defence3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less13 Defence3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less9 Defence1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Attack0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal6 Attack4all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater5 Attack4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less6 Defence2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Equal9 Defence8 | Equal12 Defence8 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡精</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>素材意图列表索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始使最前方的单位获得3护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less10 Defence4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Defence3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Defence4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡椒粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗结束为全体在场友方恢复6hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>素材生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得两素材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Less12 Defence1</t>
-  </si>
-  <si>
-    <t>None Attack0</t>
-  </si>
-  <si>
-    <t>None Heal-2</t>
-  </si>
-  <si>
-    <t>None Heal-1</t>
-  </si>
-  <si>
-    <t>None Heal-5</t>
-  </si>
-  <si>
-    <t>Less11 Defence2</t>
-  </si>
-  <si>
-    <t>Less6 Attack5</t>
-  </si>
-  <si>
-    <t>Equal3 Defence8</t>
-  </si>
-  <si>
-    <t>Equal6 Defence8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater0 Attack1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调料包（）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淀粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始使随机单位获得8护盾，失去二hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal-2 Defence5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬面团</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肉干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有数值+1（仅仅第一份有效）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始·，所有单位防御+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始·，所有单位伤害+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有防御+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有防御+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有伤害+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有伤害+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生姜精华液</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒜水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始使所有敌方受到3伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>友方单位行动后，恢复1hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Equal1 Attack13</t>
-  </si>
-  <si>
-    <t>Equal4 Attack13</t>
-  </si>
-  <si>
-    <t>Equal7 Attack13 | Equal10 Attack13</t>
-  </si>
-  <si>
-    <t>Less10 Defence4</t>
-  </si>
-  <si>
-    <t>意图列表</t>
-  </si>
-  <si>
-    <t>霉豆腐</t>
-  </si>
-  <si>
-    <t>榴莲汁</t>
-  </si>
-  <si>
-    <t>苦瓜精</t>
-  </si>
-  <si>
-    <t>小块盐</t>
-  </si>
-  <si>
-    <t>小瓶生抽</t>
-  </si>
-  <si>
-    <t>味精</t>
-  </si>
-  <si>
-    <t>胡椒水</t>
-  </si>
-  <si>
-    <t>大碗胡椒水</t>
-  </si>
-  <si>
-    <t>注释：玩家从任何途径获取到素材的时候，从素材库中随机选取一个之前没用抽取过的id对应的素材，因为有些素材可能是只有怪物才有的，所以要做好分离</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>遗物意图列表索引</t>
-  </si>
-  <si>
-    <t>素材意图列表索引</t>
-  </si>
-  <si>
-    <t>升级后的素材意图列表索引</t>
-  </si>
-  <si>
-    <t>注释：和素材库一样，这里存的是游戏中所有遗物的定义。如果某个遗物是专门作为怪物遗物，因为他在游戏中不可能被合成成卡牌，因此素材意图置空即可</t>
-  </si>
-  <si>
-    <t>精猪后腿肉</t>
-  </si>
-  <si>
-    <t>注释：同玩家素材池</t>
-  </si>
-  <si>
-    <t>卡牌1</t>
-  </si>
-  <si>
-    <t>卡牌2</t>
-  </si>
-  <si>
-    <t>卡牌3</t>
-  </si>
-  <si>
-    <t>卡牌4</t>
-  </si>
-  <si>
-    <t>遗物列表</t>
-  </si>
-  <si>
-    <t>注释：卡牌列填写的数字，代表着组成他们的素材id。遗物列表下填写的数字，代表小怪会携带的所有遗物。两个数字之间用空格分开</t>
-  </si>
-  <si>
-    <t>同样的，当进入小怪战斗后，会抽取一个之前没抽到过的卡牌组</t>
-  </si>
-  <si>
-    <t>1 2 3</t>
-  </si>
-  <si>
-    <t>2 3</t>
-  </si>
-  <si>
-    <t>注释：同小怪池</t>
-  </si>
-  <si>
-    <t>同小怪池</t>
-  </si>
-  <si>
-    <t>索引ID</t>
-  </si>
-  <si>
-    <t>合成表</t>
-  </si>
-  <si>
-    <t>合成物</t>
-  </si>
-  <si>
-    <t>N2.1</t>
-  </si>
-  <si>
-    <t>香菇*1</t>
-  </si>
-  <si>
-    <t>n2.2</t>
-  </si>
-  <si>
-    <t>任意肉*1</t>
-  </si>
-  <si>
-    <t>N2.3</t>
-  </si>
-  <si>
-    <t>糊的肉*1</t>
-  </si>
-  <si>
-    <t>N2.4</t>
-  </si>
-  <si>
-    <t>任意水*1+盐*1</t>
-  </si>
-  <si>
-    <t>盐水</t>
-  </si>
-  <si>
-    <t>N2.5</t>
-  </si>
-  <si>
-    <t>盐水*1+任意水*1</t>
-  </si>
-  <si>
-    <t>N2.6</t>
-  </si>
-  <si>
-    <t>任意2稀有度及以上的水*1+盐*1</t>
-  </si>
-  <si>
-    <t>N2.7</t>
-  </si>
-  <si>
-    <t>N2.8</t>
-  </si>
-  <si>
-    <t>N2.9</t>
-  </si>
-  <si>
-    <t>N2.10</t>
-  </si>
-  <si>
-    <t>N2.11</t>
-  </si>
-  <si>
-    <t>N2.12</t>
-  </si>
-  <si>
-    <t>N2.13</t>
-  </si>
-  <si>
-    <t>N2.14</t>
-  </si>
-  <si>
-    <t>N2.15</t>
-  </si>
-  <si>
-    <t>N2.16</t>
-  </si>
-  <si>
-    <t>N2.17</t>
-  </si>
-  <si>
-    <t>N2.18</t>
-  </si>
-  <si>
-    <t>N2.19</t>
-  </si>
-  <si>
-    <t>N2.20</t>
-  </si>
-  <si>
-    <t>N2.21</t>
-  </si>
-  <si>
-    <t>N2.22</t>
-  </si>
-  <si>
-    <t>N2.23</t>
-  </si>
-  <si>
-    <t>N2.24</t>
-  </si>
-  <si>
-    <t>N2.25</t>
-  </si>
-  <si>
-    <t>N2.26</t>
-  </si>
-  <si>
-    <t>N2.27</t>
-  </si>
-  <si>
-    <t>N2.28</t>
-  </si>
-  <si>
-    <t>N2.29</t>
-  </si>
-  <si>
-    <t>N2.30</t>
-  </si>
-  <si>
-    <t>N2.31</t>
-  </si>
-  <si>
-    <t>N2.32</t>
-  </si>
-  <si>
-    <t>角色名字</t>
-  </si>
-  <si>
-    <t>升级所需经验</t>
-  </si>
-  <si>
-    <t>角色星级</t>
-  </si>
-  <si>
-    <t>背包里显示的图标</t>
-  </si>
-  <si>
-    <t>升级路径</t>
-  </si>
-  <si>
-    <t>特殊机制与加成</t>
-  </si>
-  <si>
-    <t>N1.0</t>
-  </si>
-  <si>
-    <t>通用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal2all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Attack3all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Attack4all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1-&gt;2-&gt;2-&gt;3-&gt;3</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>N1.1</t>
-  </si>
-  <si>
-    <t>无-&gt;无&gt;无-&gt;无</t>
-  </si>
-  <si>
-    <t>猪腿煲汤</t>
-  </si>
-  <si>
-    <t>N1.2</t>
-  </si>
-  <si>
-    <t>无-&gt;hp+3-&gt;无-&gt;无</t>
-  </si>
-  <si>
-    <t>战斗开始获得十格挡</t>
-  </si>
-  <si>
-    <t>特级精品猪油+精品猪后腿肉+咸水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意水*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无-&gt;hp+3-&gt;hp+3-&gt;hp+9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp+29,增加意图：=2/5/8/11,打2*4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特级混合精碎肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清汤*2+特级混合精碎肉蒜水肉干汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特级混合精肉饼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵炖汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1-&gt;2-&gt;2-&gt;3-&gt;5</t>
-  </si>
-  <si>
-    <t>N1.3</t>
-  </si>
-  <si>
-    <t>无-&gt;hp+3-&gt;hp+3-&gt;hp+9</t>
-  </si>
-  <si>
-    <t>hp+29,增加意图：=2/5/8/11,打2*4</t>
-  </si>
-  <si>
-    <t>海藻水+海藻气泡+海藻团块</t>
-  </si>
-  <si>
-    <t>N1.4</t>
-  </si>
-  <si>
-    <t>N1.5</t>
-  </si>
-  <si>
-    <t>N1.6</t>
-  </si>
-  <si>
-    <t>N1.7</t>
-  </si>
-  <si>
-    <t>N1.8</t>
-  </si>
-  <si>
-    <t>N1.9</t>
-  </si>
-  <si>
-    <t>N1.10</t>
-  </si>
-  <si>
-    <t>N1.11</t>
-  </si>
-  <si>
-    <t>N1.12</t>
-  </si>
-  <si>
-    <t>N1.13</t>
-  </si>
-  <si>
-    <t>N1.14</t>
-  </si>
-  <si>
-    <t>N1.15</t>
-  </si>
-  <si>
-    <t>N1.16</t>
-  </si>
-  <si>
-    <t>N1.17</t>
-  </si>
-  <si>
-    <t>N1.18</t>
-  </si>
-  <si>
-    <t>N1.19</t>
-  </si>
-  <si>
-    <t>N1.20</t>
-  </si>
-  <si>
-    <t>N1.21</t>
-  </si>
-  <si>
-    <t>N1.22</t>
-  </si>
-  <si>
-    <t>N1.23</t>
-  </si>
-  <si>
-    <t>N1.24</t>
-  </si>
-  <si>
-    <t>N1.25</t>
-  </si>
-  <si>
-    <t>N1.26</t>
-  </si>
-  <si>
-    <t>N1.27</t>
-  </si>
-  <si>
-    <t>N1.28</t>
-  </si>
-  <si>
-    <t>N1.29</t>
-  </si>
-  <si>
-    <t>N1.30</t>
-  </si>
-  <si>
-    <t>N1.31</t>
-  </si>
-  <si>
-    <t>N1.32</t>
-  </si>
-  <si>
-    <t>N1.33</t>
-  </si>
-  <si>
-    <t>N1.34</t>
-  </si>
-  <si>
-    <t>N1.35</t>
-  </si>
-  <si>
-    <t>N1.36</t>
-  </si>
-  <si>
-    <t>N1.37</t>
-  </si>
-  <si>
-    <t>N1.38</t>
-  </si>
-  <si>
-    <t>N1.39</t>
-  </si>
-  <si>
-    <t>N1.40</t>
-  </si>
-  <si>
-    <t>N1.41</t>
-  </si>
-  <si>
-    <t>N1.42</t>
-  </si>
-  <si>
-    <t>N1.43</t>
-  </si>
-  <si>
-    <t>N1.44</t>
-  </si>
-  <si>
-    <t>N1.45</t>
-  </si>
-  <si>
-    <t>N1.46</t>
-  </si>
-  <si>
-    <t>N1.47</t>
-  </si>
-  <si>
-    <t>N1.48</t>
-  </si>
-  <si>
-    <t>N1.49</t>
-  </si>
-  <si>
-    <t>N1.50</t>
-  </si>
-  <si>
-    <t>N1.51</t>
-  </si>
-  <si>
-    <t>N1.52</t>
-  </si>
-  <si>
-    <t>N1.53</t>
-  </si>
-  <si>
-    <t>N1.54</t>
-  </si>
-  <si>
-    <t>N1.55</t>
-  </si>
-  <si>
-    <t>N1.56</t>
-  </si>
-  <si>
-    <t>N1.57</t>
-  </si>
-  <si>
-    <t>N1.58</t>
-  </si>
-  <si>
-    <t>N1.59</t>
-  </si>
-  <si>
-    <t>N1.60</t>
-  </si>
-  <si>
-    <t>N1.61</t>
-  </si>
-  <si>
-    <t>N1.62</t>
-  </si>
-  <si>
-    <t>N1.63</t>
-  </si>
-  <si>
-    <t>N1.64</t>
-  </si>
-  <si>
-    <t>N1.65</t>
-  </si>
-  <si>
-    <t>N1.66</t>
-  </si>
-  <si>
-    <t>N1.67</t>
-  </si>
-  <si>
-    <t>N1.68</t>
-  </si>
-  <si>
-    <t>N1.69</t>
-  </si>
-  <si>
-    <t>N1.70</t>
-  </si>
-  <si>
-    <t>N1.71</t>
-  </si>
-  <si>
-    <t>N1.72</t>
-  </si>
-  <si>
-    <t>N1.73</t>
-  </si>
-  <si>
-    <t>N1.74</t>
-  </si>
-  <si>
-    <t>N1.75</t>
-  </si>
-  <si>
-    <t>N1.76</t>
-  </si>
-  <si>
-    <t>N1.77</t>
-  </si>
-  <si>
-    <t>N1.78</t>
-  </si>
-  <si>
-    <t>N1.79</t>
-  </si>
-  <si>
-    <t>N1.80</t>
-  </si>
-  <si>
-    <t>N1.81</t>
-  </si>
-  <si>
-    <t>N1.82</t>
-  </si>
-  <si>
-    <t>N1.83</t>
-  </si>
-  <si>
-    <t>N1.84</t>
-  </si>
-  <si>
-    <t>N1.85</t>
-  </si>
-  <si>
-    <t>N1.86</t>
-  </si>
-  <si>
-    <t>N1.87</t>
-  </si>
-  <si>
-    <t>N1.88</t>
-  </si>
-  <si>
-    <t>N1.89</t>
-  </si>
-  <si>
-    <t>N1.90</t>
-  </si>
-  <si>
-    <t>N1.91</t>
-  </si>
-  <si>
-    <t>N1.92</t>
-  </si>
-  <si>
-    <t>N1.93</t>
-  </si>
-  <si>
-    <t>N1.94</t>
-  </si>
-  <si>
-    <t>N1.95</t>
-  </si>
-  <si>
-    <t>N1.96</t>
-  </si>
-  <si>
-    <t>N1.97</t>
-  </si>
-  <si>
-    <t>N1.98</t>
-  </si>
-  <si>
-    <t>N1.99</t>
-  </si>
-  <si>
-    <t>N1.100</t>
-  </si>
-  <si>
-    <t>N1.101</t>
-  </si>
-  <si>
-    <t>N1.102</t>
-  </si>
-  <si>
-    <t>N1.103</t>
-  </si>
-  <si>
-    <t>N1.104</t>
-  </si>
-  <si>
-    <t>N1.105</t>
-  </si>
-  <si>
-    <t>N1.106</t>
-  </si>
-  <si>
-    <t>N1.107</t>
-  </si>
-  <si>
-    <t>N1.108</t>
-  </si>
-  <si>
-    <t>N1.109</t>
-  </si>
-  <si>
-    <t>N1.110</t>
-  </si>
-  <si>
-    <t>N1.111</t>
-  </si>
-  <si>
-    <t>N1.112</t>
-  </si>
-  <si>
-    <t>N1.113</t>
-  </si>
-  <si>
-    <t>N1.114</t>
-  </si>
-  <si>
-    <t>N1.115</t>
-  </si>
-  <si>
-    <t>N1.116</t>
-  </si>
-  <si>
-    <t>N1.117</t>
-  </si>
-  <si>
-    <t>N1.118</t>
-  </si>
-  <si>
-    <t>N1.119</t>
-  </si>
-  <si>
-    <t>N1.120</t>
-  </si>
-  <si>
-    <t>N1.121</t>
-  </si>
-  <si>
-    <t>N1.122</t>
-  </si>
-  <si>
-    <t>N1.123</t>
-  </si>
-  <si>
-    <t>N1.124</t>
-  </si>
-  <si>
-    <t>N1.125</t>
-  </si>
-  <si>
-    <t>N1.126</t>
-  </si>
-  <si>
-    <t>N1.127</t>
-  </si>
-  <si>
-    <t>N1.128</t>
-  </si>
-  <si>
-    <t>N1.129</t>
-  </si>
-  <si>
-    <t>N1.130</t>
-  </si>
-  <si>
-    <t>N1.131</t>
-  </si>
-  <si>
-    <t>N1.132</t>
-  </si>
-  <si>
-    <t>N1.133</t>
-  </si>
-  <si>
-    <t>N1.134</t>
-  </si>
-  <si>
-    <t>N1.135</t>
-  </si>
-  <si>
-    <t>N1.136</t>
-  </si>
-  <si>
-    <t>N1.137</t>
-  </si>
-  <si>
-    <t>N1.138</t>
-  </si>
-  <si>
-    <t>N1.139</t>
-  </si>
-  <si>
-    <t>N1.140</t>
-  </si>
-  <si>
-    <t>N1.141</t>
-  </si>
-  <si>
-    <t>N1.142</t>
-  </si>
-  <si>
-    <t>N1.143</t>
-  </si>
-  <si>
-    <t>N1.144</t>
-  </si>
-  <si>
-    <t>N1.145</t>
-  </si>
-  <si>
-    <t>N1.146</t>
-  </si>
-  <si>
-    <t>N1.147</t>
-  </si>
-  <si>
-    <t>N1.148</t>
-  </si>
-  <si>
-    <t>N1.149</t>
-  </si>
-  <si>
-    <t>N1.150</t>
-  </si>
-  <si>
-    <t>N1.151</t>
-  </si>
-  <si>
-    <t>N1.152</t>
-  </si>
-  <si>
-    <t>N1.153</t>
-  </si>
-  <si>
-    <t>N1.154</t>
-  </si>
-  <si>
-    <t>N1.155</t>
-  </si>
-  <si>
-    <t>N1.156</t>
-  </si>
-  <si>
-    <t>N1.157</t>
-  </si>
-  <si>
-    <t>N1.158</t>
-  </si>
-  <si>
-    <t>N1.159</t>
-  </si>
-  <si>
-    <t>N1.160</t>
-  </si>
-  <si>
-    <t>N1.161</t>
-  </si>
-  <si>
-    <t>N1.162</t>
-  </si>
-  <si>
-    <t>N1.163</t>
-  </si>
-  <si>
-    <t>N1.164</t>
-  </si>
-  <si>
-    <t>N1.165</t>
-  </si>
-  <si>
-    <t>N1.166</t>
-  </si>
-  <si>
-    <t>N1.167</t>
-  </si>
-  <si>
-    <t>N1.168</t>
-  </si>
-  <si>
-    <t>N1.169</t>
-  </si>
-  <si>
-    <t>N1.170</t>
-  </si>
-  <si>
-    <t>N1.171</t>
-  </si>
-  <si>
-    <t>N1.172</t>
-  </si>
-  <si>
-    <t>N1.173</t>
-  </si>
-  <si>
-    <t>N1.174</t>
-  </si>
-  <si>
-    <t>N1.175</t>
-  </si>
-  <si>
-    <t>N1.176</t>
-  </si>
-  <si>
-    <t>N1.177</t>
-  </si>
-  <si>
-    <t>N1.178</t>
-  </si>
-  <si>
-    <t>N1.179</t>
-  </si>
-  <si>
-    <t>N1.180</t>
-  </si>
-  <si>
-    <t>N1.181</t>
-  </si>
-  <si>
-    <t>N1.182</t>
-  </si>
-  <si>
-    <t>N1.183</t>
-  </si>
-  <si>
-    <t>N1.184</t>
-  </si>
-  <si>
-    <t>N1.185</t>
-  </si>
-  <si>
-    <t>N1.186</t>
-  </si>
-  <si>
-    <t>N1.187</t>
-  </si>
-  <si>
-    <t>N1.188</t>
-  </si>
-  <si>
-    <t>N1.189</t>
-  </si>
-  <si>
-    <t>N1.190</t>
-  </si>
-  <si>
-    <t>N1.191</t>
-  </si>
-  <si>
-    <t>N1.192</t>
-  </si>
-  <si>
-    <t>N1.193</t>
-  </si>
-  <si>
-    <t>N1.194</t>
-  </si>
-  <si>
-    <t>N1.195</t>
-  </si>
-  <si>
-    <t>N1.196</t>
-  </si>
-  <si>
-    <t>N1.197</t>
-  </si>
-  <si>
-    <t>N1.198</t>
-  </si>
-  <si>
-    <t>N1.199</t>
-  </si>
-  <si>
-    <t>N1.200</t>
-  </si>
-  <si>
-    <t>N1.201</t>
-  </si>
-  <si>
-    <t>N1.202</t>
-  </si>
-  <si>
-    <t>N1.203</t>
-  </si>
-  <si>
-    <t>N1.204</t>
-  </si>
-  <si>
-    <t>N1.205</t>
-  </si>
-  <si>
-    <t>N1.206</t>
-  </si>
-  <si>
-    <t>N1.207</t>
-  </si>
-  <si>
-    <t>N1.208</t>
-  </si>
-  <si>
-    <t>N1.209</t>
-  </si>
-  <si>
-    <t>N1.210</t>
-  </si>
-  <si>
-    <t>N1.211</t>
-  </si>
-  <si>
-    <t>N1.212</t>
-  </si>
-  <si>
-    <t>N1.213</t>
-  </si>
-  <si>
-    <t>N1.214</t>
-  </si>
-  <si>
-    <t>N1.215</t>
-  </si>
-  <si>
-    <t>N1.216</t>
-  </si>
-  <si>
-    <t>N1.217</t>
-  </si>
-  <si>
-    <t>N1.218</t>
-  </si>
-  <si>
-    <t>N1.219</t>
-  </si>
-  <si>
-    <t>N1.220</t>
-  </si>
-  <si>
-    <t>N1.221</t>
-  </si>
-  <si>
-    <t>N1.222</t>
-  </si>
-  <si>
-    <t>N1.223</t>
-  </si>
-  <si>
-    <t>N1.224</t>
-  </si>
-  <si>
-    <t>N1.225</t>
-  </si>
-  <si>
-    <t>N1.226</t>
-  </si>
-  <si>
-    <t>N1.227</t>
-  </si>
-  <si>
-    <t>N1.228</t>
-  </si>
-  <si>
-    <t>N1.229</t>
-  </si>
-  <si>
-    <t>N1.230</t>
-  </si>
-  <si>
-    <t>N1.231</t>
-  </si>
-  <si>
-    <t>N1.232</t>
-  </si>
-  <si>
-    <t>N1.233</t>
-  </si>
-  <si>
-    <t>N1.234</t>
-  </si>
-  <si>
-    <t>N1.235</t>
-  </si>
-  <si>
-    <t>N1.236</t>
-  </si>
-  <si>
-    <t>N1.237</t>
-  </si>
-  <si>
-    <t>N1.238</t>
-  </si>
-  <si>
-    <t>N1.239</t>
-  </si>
-  <si>
-    <t>N1.240</t>
-  </si>
-  <si>
-    <t>N1.241</t>
-  </si>
-  <si>
-    <t>N1.242</t>
-  </si>
-  <si>
-    <t>N1.243</t>
-  </si>
-  <si>
-    <t>N1.244</t>
-  </si>
-  <si>
-    <t>N1.245</t>
-  </si>
-  <si>
-    <t>N1.246</t>
-  </si>
-  <si>
-    <t>N1.247</t>
-  </si>
-  <si>
-    <t>N1.248</t>
-  </si>
-  <si>
-    <t>N1.249</t>
-  </si>
-  <si>
-    <t>N1.250</t>
-  </si>
-  <si>
-    <t>N1.251</t>
-  </si>
-  <si>
-    <t>N1.252</t>
-  </si>
-  <si>
-    <t>N1.253</t>
-  </si>
-  <si>
-    <t>N1.254</t>
-  </si>
-  <si>
-    <t>N1.255</t>
-  </si>
-  <si>
-    <t>N1.256</t>
-  </si>
-  <si>
-    <t>N1.257</t>
-  </si>
-  <si>
-    <t>N1.258</t>
-  </si>
-  <si>
-    <t>N1.259</t>
-  </si>
-  <si>
-    <t>N1.260</t>
-  </si>
-  <si>
-    <t>N1.261</t>
-  </si>
-  <si>
-    <t>N1.262</t>
-  </si>
-  <si>
-    <t>N1.263</t>
-  </si>
-  <si>
-    <t>N1.264</t>
-  </si>
-  <si>
-    <t>N1.265</t>
-  </si>
-  <si>
-    <t>N1.266</t>
-  </si>
-  <si>
-    <t>N1.267</t>
-  </si>
-  <si>
-    <t>N1.268</t>
-  </si>
-  <si>
-    <t>N1.269</t>
-  </si>
-  <si>
-    <t>N1.270</t>
-  </si>
-  <si>
-    <t>N1.271</t>
-  </si>
-  <si>
-    <t>N1.272</t>
-  </si>
-  <si>
-    <t>N1.273</t>
-  </si>
-  <si>
-    <t>N1.274</t>
-  </si>
-  <si>
-    <t>N1.275</t>
-  </si>
-  <si>
-    <t>N1.276</t>
-  </si>
-  <si>
-    <t>N1.277</t>
-  </si>
-  <si>
-    <t>N1.278</t>
-  </si>
-  <si>
-    <t>N1.279</t>
-  </si>
-  <si>
-    <t>N1.280</t>
-  </si>
-  <si>
-    <t>N1.281</t>
-  </si>
-  <si>
-    <t>N1.282</t>
-  </si>
-  <si>
-    <t>N1.283</t>
-  </si>
-  <si>
-    <t>N1.284</t>
-  </si>
-  <si>
-    <t>N1.285</t>
-  </si>
-  <si>
-    <t>N1.286</t>
-  </si>
-  <si>
-    <t>N1.287</t>
-  </si>
-  <si>
-    <t>N1.288</t>
-  </si>
-  <si>
-    <t>N1.289</t>
-  </si>
-  <si>
-    <t>N1.290</t>
-  </si>
-  <si>
-    <t>N1.291</t>
-  </si>
-  <si>
-    <t>N1.292</t>
-  </si>
-  <si>
-    <t>N1.293</t>
-  </si>
-  <si>
-    <t>N1.294</t>
-  </si>
-  <si>
-    <t>N1.295</t>
-  </si>
-  <si>
-    <t>N1.296</t>
-  </si>
-  <si>
-    <t>N1.297</t>
-  </si>
-  <si>
-    <t>N1.298</t>
-  </si>
-  <si>
-    <t>N1.299</t>
-  </si>
-  <si>
-    <t>N1.300</t>
-  </si>
-  <si>
-    <t>N1.301</t>
-  </si>
-  <si>
-    <t>N1.302</t>
-  </si>
-  <si>
-    <t>N1.303</t>
-  </si>
-  <si>
-    <t>N1.304</t>
-  </si>
-  <si>
-    <t>N1.305</t>
-  </si>
-  <si>
-    <t>N1.306</t>
-  </si>
-  <si>
-    <t>N1.307</t>
-  </si>
-  <si>
-    <t>N1.308</t>
-  </si>
-  <si>
-    <t>N1.309</t>
-  </si>
-  <si>
-    <t>N1.310</t>
-  </si>
-  <si>
-    <t>N1.311</t>
-  </si>
-  <si>
-    <t>N1.312</t>
-  </si>
-  <si>
-    <t>N1.313</t>
-  </si>
-  <si>
-    <t>N1.314</t>
-  </si>
-  <si>
-    <t>N1.315</t>
-  </si>
-  <si>
-    <t>N1.316</t>
-  </si>
-  <si>
-    <t>N1.317</t>
-  </si>
-  <si>
-    <t>N1.318</t>
-  </si>
-  <si>
-    <t>N1.319</t>
-  </si>
-  <si>
-    <t>N1.320</t>
-  </si>
-  <si>
-    <t>N1.321</t>
-  </si>
-  <si>
-    <t>N1.322</t>
-  </si>
-  <si>
-    <t>N1.323</t>
-  </si>
-  <si>
-    <t>N1.324</t>
-  </si>
-  <si>
-    <t>N1.325</t>
-  </si>
-  <si>
-    <t>N1.326</t>
-  </si>
-  <si>
-    <t>Greater5 Attack2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less4 Attack2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less4 Attack3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Greater8 Attack1*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal6 Attack4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack0*3 | Equal12 Attack0*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack1*3 | Equal12 Attack1*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less6 Attack3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal6 Attack8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Greater3 Attack2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack1*4 | Equal12 Attack1*4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>海洋混混浓汤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猪腿煲汤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less7 Attack5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Greater5 Attack2*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Greater0 Attack2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal6 Attack16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal7 Attack1 | Equal9 Attack1 | Equal11 Attack1 | Equal6 Attack1*4 | Equal12 Attack1*4 | Equal1 Attack1*4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal1 Attack1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Heal2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Attack3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Defence3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less13 Defence3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束所有伤害+1，hp+30,hp&lt;15时hp-10且获得15护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特级混合精肉饼+硬面团+肉干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意肉饼+任意鸡蛋+任意水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香料炖汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生姜精华液+蒜水+胡椒粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香料炖汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp+15,每次行动执行意图执行两次</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>None Heal3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Heal4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Heal0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Heal6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Heal1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less9 Defence1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None Attack0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equal6 Attack4all</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Greater5 Attack4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less6 Defence2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Equal9 Defence8 | Equal12 Defence8 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1972,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -2137,7 +2339,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>558</v>
       </c>
       <c r="C8" s="5">
         <v>10</v>
@@ -2177,7 +2379,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>556</v>
       </c>
       <c r="C10" s="5">
         <v>3</v>
@@ -2456,9 +2658,6 @@
       <c r="C24" s="5">
         <v>10</v>
       </c>
-      <c r="D24" s="2">
-        <v>5</v>
-      </c>
       <c r="E24" s="5">
         <v>45</v>
       </c>
@@ -2556,9 +2755,6 @@
       <c r="C29" s="5">
         <v>15</v>
       </c>
-      <c r="D29" s="2">
-        <v>5</v>
-      </c>
       <c r="E29" s="5">
         <v>55</v>
       </c>
@@ -2584,6 +2780,376 @@
       </c>
       <c r="F30" s="5">
         <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <v>59</v>
+      </c>
+      <c r="F31" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="5">
+        <v>61</v>
+      </c>
+      <c r="F32" s="5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C33" s="2">
+        <v>5</v>
+      </c>
+      <c r="E33" s="5">
+        <v>63</v>
+      </c>
+      <c r="F33" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="5">
+        <v>65</v>
+      </c>
+      <c r="F34" s="5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="C35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="5">
+        <v>67</v>
+      </c>
+      <c r="F35" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="5">
+        <v>69</v>
+      </c>
+      <c r="F36" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5">
+        <v>71</v>
+      </c>
+      <c r="F37" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5">
+        <v>73</v>
+      </c>
+      <c r="F38" s="5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="E39" s="5">
+        <v>75</v>
+      </c>
+      <c r="F39" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="E40" s="5">
+        <v>77</v>
+      </c>
+      <c r="F40" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="E41" s="5">
+        <v>79</v>
+      </c>
+      <c r="F41" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
+      <c r="E42" s="5">
+        <v>81</v>
+      </c>
+      <c r="F42" s="5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="E43" s="5">
+        <v>83</v>
+      </c>
+      <c r="F43" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="E44" s="5">
+        <v>85</v>
+      </c>
+      <c r="F44" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="E45" s="5">
+        <v>87</v>
+      </c>
+      <c r="F45" s="5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="E46" s="5">
+        <v>89</v>
+      </c>
+      <c r="F46" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="E47" s="5">
+        <v>91</v>
+      </c>
+      <c r="F47" s="5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
+      <c r="E48" s="5">
+        <v>93</v>
+      </c>
+      <c r="F48" s="5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="E49" s="5">
+        <v>95</v>
+      </c>
+      <c r="F49" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="E50" s="5">
+        <v>97</v>
+      </c>
+      <c r="F50" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="E51" s="5">
+        <v>99</v>
+      </c>
+      <c r="F51" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="E52" s="5">
+        <v>101</v>
+      </c>
+      <c r="F52" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E53" s="5">
+        <v>103</v>
+      </c>
+      <c r="F53" s="5">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E54" s="5">
+        <v>105</v>
+      </c>
+      <c r="F54" s="5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E55" s="5">
+        <v>107</v>
+      </c>
+      <c r="F55" s="5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E56" s="5">
+        <v>109</v>
+      </c>
+      <c r="F56" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E57" s="5">
+        <v>111</v>
+      </c>
+      <c r="F57" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E58" s="5">
+        <v>113</v>
+      </c>
+      <c r="F58" s="5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E59" s="5">
+        <v>115</v>
+      </c>
+      <c r="F59" s="5">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E60" s="5">
+        <v>117</v>
+      </c>
+      <c r="F60" s="5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E61" s="5">
+        <v>119</v>
+      </c>
+      <c r="F61" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E62" s="5">
+        <v>121</v>
+      </c>
+      <c r="F62" s="5">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2603,21 +3169,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -2625,10 +3191,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -2636,10 +3202,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -2647,21 +3213,21 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
@@ -2669,10 +3235,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
         <v>36</v>
@@ -2680,132 +3246,132 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2822,2199 +3388,2256 @@
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="26.5546875" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" customWidth="1"/>
-    <col min="7" max="7" width="35.44140625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="80" customWidth="1"/>
     <col min="8" max="8" width="44.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
         <v>141</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>142</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>143</v>
       </c>
-      <c r="E1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G1" t="s">
-        <v>146</v>
-      </c>
       <c r="H1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
         <v>147</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>148</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>149</v>
-      </c>
-      <c r="D2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>551</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" t="s">
         <v>154</v>
-      </c>
-      <c r="F3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>560</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F4" t="s">
-        <v>160</v>
+        <v>553</v>
       </c>
       <c r="G4" t="s">
-        <v>161</v>
+        <v>554</v>
       </c>
       <c r="H4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C5" t="s">
+        <v>551</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>157</v>
+      </c>
+      <c r="F5" t="s">
+        <v>553</v>
+      </c>
+      <c r="G5" t="s">
+        <v>555</v>
+      </c>
+      <c r="H5" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>157</v>
+      </c>
+      <c r="B6" t="s">
+        <v>559</v>
+      </c>
+      <c r="C6" t="s">
+        <v>560</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>158</v>
+      </c>
+      <c r="F6" t="s">
+        <v>553</v>
+      </c>
+      <c r="G6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H6" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>158</v>
+      </c>
+      <c r="B7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C7" t="s">
+        <v>551</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>159</v>
+      </c>
+      <c r="F7" t="s">
+        <v>553</v>
+      </c>
+      <c r="G7" t="s">
+        <v>567</v>
+      </c>
+      <c r="H7" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>160</v>
+      </c>
+      <c r="H8" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E11" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E17" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E25" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E26" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E28" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E29" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E30" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E37" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E42" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E46" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E47" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E48" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E50" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E53" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E54" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E55" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E56" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E57" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E58" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E59" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E60" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E61" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E62" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E63" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E64" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E65" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E66" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E67" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E68" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E69" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E70" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E71" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E72" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E73" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E74" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E75" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E76" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E77" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E78" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E79" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E80" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E81" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E82" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E83" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E84" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E85" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E86" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E87" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E88" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E89" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E90" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E91" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E92" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E93" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E94" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E95" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E96" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E97" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E98" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E99" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E100" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E101" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E102" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E103" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E104" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E105" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E106" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E107" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E108" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E109" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E110" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E111" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="E112" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E113" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E114" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E115" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E116" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E117" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E118" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E119" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E120" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E121" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E122" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E123" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="E124" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E125" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E126" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E127" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E128" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E129" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E130" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E131" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E132" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E133" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E134" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E135" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E136" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E137" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E138" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E139" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E140" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E141" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E142" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E143" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E144" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E145" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E146" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E147" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E148" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E149" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E150" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E151" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E152" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E153" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E154" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E155" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E156" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E157" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E158" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E159" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E160" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E161" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E162" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E163" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E164" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E165" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E166" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E167" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E168" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E169" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E170" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E171" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E172" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E173" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E174" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E175" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E176" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="177" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E177" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="178" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E178" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="179" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E179" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="180" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E180" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="181" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E181" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="182" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E182" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="183" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E183" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="184" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E184" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="185" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E185" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="186" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E186" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="187" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E187" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="188" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E188" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="189" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E189" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="190" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E190" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="191" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E191" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="192" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E192" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="193" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E193" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="194" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E194" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="195" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E195" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="196" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E196" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="197" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E197" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="198" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E198" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="199" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E199" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="200" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E200" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="201" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E201" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="202" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E202" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="203" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E203" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="204" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E204" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="205" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E205" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="206" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E206" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="207" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E207" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="208" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E208" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="209" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E209" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="210" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E210" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="211" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E211" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="212" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E212" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="213" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E213" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="214" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E214" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="215" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E215" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="216" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E216" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="217" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E217" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="218" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E218" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="219" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E219" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="220" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E220" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="221" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E221" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="222" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E222" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="223" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E223" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="224" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E224" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="225" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E225" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="226" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E226" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="227" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E227" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="228" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E228" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="229" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E229" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="230" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E230" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="231" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E231" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="232" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E232" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="233" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E233" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="234" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E234" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="235" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E235" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="236" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E236" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="237" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E237" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="238" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E238" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="239" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E239" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="240" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E240" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="241" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E241" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="242" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E242" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="243" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E243" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="244" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E244" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="245" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E245" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="246" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E246" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="247" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E247" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="248" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E248" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="249" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E249" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="250" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E250" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="251" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E251" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="252" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E252" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="253" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E253" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="254" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E254" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="255" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E255" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="256" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E256" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="257" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E257" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="258" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E258" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="259" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E259" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="260" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E260" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="261" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E261" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="262" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E262" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="263" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E263" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="264" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E264" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="265" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E265" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="266" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E266" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="267" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E267" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="268" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E268" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="269" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E269" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="270" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E270" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="271" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E271" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="272" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E272" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="273" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E273" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="274" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E274" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="275" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E275" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="276" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E276" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="277" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E277" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="278" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E278" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="279" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E279" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="280" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E280" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="281" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E281" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="282" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E282" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="283" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E283" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="284" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E284" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="285" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E285" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="286" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E286" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="287" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E287" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="288" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E288" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="289" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E289" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="290" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E290" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="291" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E291" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="292" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E292" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="293" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E293" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="294" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E294" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="295" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E295" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="296" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E296" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="297" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E297" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="298" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E298" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="299" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E299" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="300" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E300" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="301" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E301" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="302" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E302" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="303" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E303" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="304" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E304" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="305" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E305" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="306" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E306" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="307" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E307" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="308" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E308" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="309" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E309" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="310" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E310" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="311" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E311" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="312" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E312" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="313" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E313" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="314" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E314" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="315" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E315" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="316" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E316" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="317" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E317" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="318" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E318" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="319" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E319" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="320" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E320" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="321" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E321" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="322" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E322" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="323" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E323" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="324" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E324" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="325" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E325" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="326" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E326" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="327" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E327" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -5025,7 +5648,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -5061,10 +5684,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5072,10 +5695,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5086,7 +5709,7 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5094,10 +5717,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5114,7 +5737,7 @@
         <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5131,7 +5754,7 @@
         <v>43</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5150,7 +5773,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>45</v>
@@ -5164,7 +5787,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5172,10 +5795,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -5192,7 +5815,7 @@
         <v>43</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -5209,7 +5832,7 @@
         <v>43</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -5228,10 +5851,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -5242,7 +5865,7 @@
         <v>51</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5250,10 +5873,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -5270,7 +5893,7 @@
         <v>43</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5278,7 +5901,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>47</v>
@@ -5287,7 +5910,7 @@
         <v>48</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5295,7 +5918,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>53</v>
@@ -5312,10 +5935,10 @@
         <v>52</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D21" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5326,10 +5949,10 @@
         <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D22" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5337,13 +5960,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D23" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5351,7 +5974,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>55</v>
@@ -5365,7 +5988,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>55</v>
@@ -5379,7 +6002,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5387,7 +6010,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5395,10 +6018,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5406,10 +6029,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5417,10 +6040,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D30" t="s">
         <v>57</v>
@@ -5431,13 +6054,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D31" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5448,7 +6071,7 @@
         <v>57</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -5459,7 +6082,7 @@
         <v>57</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>58</v>
+        <v>526</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -5467,7 +6090,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -5475,7 +6098,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -5483,7 +6106,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -5491,30 +6114,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="5"/>
+      <c r="B38" s="5" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="5"/>
+      <c r="B39" s="5" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -5522,10 +6149,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -5533,7 +6160,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -5541,7 +6168,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5552,7 +6179,7 @@
         <v>57</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -5563,7 +6190,7 @@
         <v>57</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -5571,10 +6198,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -5582,10 +6209,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -5593,10 +6220,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -5604,10 +6231,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -5615,10 +6242,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -5626,10 +6253,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -5650,13 +6277,13 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" t="s">
         <v>65</v>
       </c>
-      <c r="D54" t="s">
-        <v>66</v>
-      </c>
       <c r="E54" s="8" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -5665,13 +6292,13 @@
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" t="s">
         <v>65</v>
       </c>
-      <c r="D55" t="s">
-        <v>66</v>
-      </c>
       <c r="E55" s="8" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -5680,13 +6307,13 @@
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D56" t="s">
         <v>67</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -5695,13 +6322,13 @@
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" t="s">
         <v>67</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -5709,10 +6336,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>70</v>
+        <v>519</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -5720,23 +6347,1056 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="5"/>
+      <c r="B71" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <v>255</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5761,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5769,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -5780,7 +7440,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -5791,7 +7451,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -5802,7 +7462,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -5813,7 +7473,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -5824,7 +7484,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -5835,7 +7495,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -5846,7 +7506,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -5874,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6080,12 +7740,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="26.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="23.77734375" style="1" customWidth="1"/>
@@ -6096,22 +7756,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>85</v>
+      <c r="G1" s="1" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6119,10 +7782,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="1">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -6133,8 +7793,598 @@
       <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D4" s="1">
+        <v>59</v>
+      </c>
+      <c r="E4" s="1">
         <v>60</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D5" s="1">
+        <v>61</v>
+      </c>
+      <c r="E5" s="1">
+        <v>62</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D6" s="1">
+        <v>63</v>
+      </c>
+      <c r="E6" s="1">
+        <v>64</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D7" s="1">
+        <v>65</v>
+      </c>
+      <c r="E7" s="1">
+        <v>66</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D8" s="1">
+        <v>67</v>
+      </c>
+      <c r="E8" s="1">
+        <v>68</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D9" s="1">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1">
+        <v>70</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D10" s="1">
+        <v>71</v>
+      </c>
+      <c r="E10" s="1">
+        <v>72</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D11" s="1">
+        <v>73</v>
+      </c>
+      <c r="E11" s="1">
+        <v>74</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" s="1">
+        <v>75</v>
+      </c>
+      <c r="E12" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" s="1">
+        <v>77</v>
+      </c>
+      <c r="E13" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" s="1">
+        <v>79</v>
+      </c>
+      <c r="E14" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" s="1">
+        <v>81</v>
+      </c>
+      <c r="E15" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D16" s="1">
+        <v>83</v>
+      </c>
+      <c r="E16" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="1">
+        <v>85</v>
+      </c>
+      <c r="E17" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="1">
+        <v>87</v>
+      </c>
+      <c r="E18" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D19" s="1">
+        <v>89</v>
+      </c>
+      <c r="E19" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="1">
+        <v>91</v>
+      </c>
+      <c r="E20" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D21" s="1">
+        <v>93</v>
+      </c>
+      <c r="E21" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D22" s="1">
+        <v>95</v>
+      </c>
+      <c r="E22" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D23" s="1">
+        <v>97</v>
+      </c>
+      <c r="E23" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D24" s="1">
+        <v>99</v>
+      </c>
+      <c r="E24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D25" s="1">
+        <v>101</v>
+      </c>
+      <c r="E25" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D26" s="1">
+        <v>103</v>
+      </c>
+      <c r="E26" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D27" s="1">
+        <v>105</v>
+      </c>
+      <c r="E27" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D28" s="1">
+        <v>107</v>
+      </c>
+      <c r="E28" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="1">
+        <v>109</v>
+      </c>
+      <c r="E29" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D30" s="1">
+        <v>111</v>
+      </c>
+      <c r="E30" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D31" s="1">
+        <v>113</v>
+      </c>
+      <c r="E31" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D32" s="1">
+        <v>115</v>
+      </c>
+      <c r="E32" s="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D33" s="1">
+        <v>117</v>
+      </c>
+      <c r="E33" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D34" s="1">
+        <v>119</v>
+      </c>
+      <c r="E34" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D35" s="1">
+        <v>121</v>
+      </c>
+      <c r="E35" s="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D36" s="1">
+        <v>123</v>
+      </c>
+      <c r="E36" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D37" s="1">
+        <v>125</v>
+      </c>
+      <c r="E37" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D38" s="1">
+        <v>127</v>
+      </c>
+      <c r="E38" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D39" s="1">
+        <v>129</v>
+      </c>
+      <c r="E39" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D40" s="1">
+        <v>131</v>
+      </c>
+      <c r="E40" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D41" s="1">
+        <v>133</v>
+      </c>
+      <c r="E41" s="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D42" s="1">
+        <v>135</v>
+      </c>
+      <c r="E42" s="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D43" s="1">
+        <v>137</v>
+      </c>
+      <c r="E43" s="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D44" s="1">
+        <v>139</v>
+      </c>
+      <c r="E44" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D45" s="1">
+        <v>141</v>
+      </c>
+      <c r="E45" s="1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D46" s="1">
+        <v>143</v>
+      </c>
+      <c r="E46" s="1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D47" s="1">
+        <v>145</v>
+      </c>
+      <c r="E47" s="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D48" s="1">
+        <v>147</v>
+      </c>
+      <c r="E48" s="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D49" s="1">
+        <v>149</v>
+      </c>
+      <c r="E49" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D50" s="1">
+        <v>151</v>
+      </c>
+      <c r="E50" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D51" s="1">
+        <v>153</v>
+      </c>
+      <c r="E51" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D52" s="1">
+        <v>155</v>
+      </c>
+      <c r="E52" s="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D53" s="1">
+        <v>157</v>
+      </c>
+      <c r="E53" s="1">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D54" s="1">
+        <v>159</v>
+      </c>
+      <c r="E54" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D55" s="1">
+        <v>161</v>
+      </c>
+      <c r="E55" s="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D56" s="1">
+        <v>163</v>
+      </c>
+      <c r="E56" s="1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D57" s="1">
+        <v>165</v>
+      </c>
+      <c r="E57" s="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D58" s="1">
+        <v>167</v>
+      </c>
+      <c r="E58" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D59" s="1">
+        <v>169</v>
+      </c>
+      <c r="E59" s="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D60" s="1">
+        <v>171</v>
+      </c>
+      <c r="E60" s="1">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D61" s="1">
+        <v>173</v>
+      </c>
+      <c r="E61" s="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D62" s="1">
+        <v>175</v>
+      </c>
+      <c r="E62" s="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D63" s="1">
+        <v>177</v>
+      </c>
+      <c r="E63" s="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="1">
+        <v>179</v>
+      </c>
+      <c r="E64" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D65" s="1">
+        <v>181</v>
+      </c>
+      <c r="E65" s="1">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -6145,7 +8395,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.44140625" customWidth="1"/>
@@ -6156,7 +8406,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6164,7 +8414,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6172,7 +8422,78 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -6199,25 +8520,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -6225,10 +8546,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -6242,10 +8563,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6253,22 +8574,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>89</v>
       </c>
-      <c r="D1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" t="s">
-        <v>92</v>
-      </c>
       <c r="G1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6276,7 +8597,23 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -6287,7 +8624,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.77734375" customWidth="1"/>
@@ -6295,25 +8632,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>89</v>
       </c>
-      <c r="D1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" t="s">
-        <v>92</v>
-      </c>
       <c r="G1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,7 +8658,15 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>497</v>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Documents/全局配置表.xlsx
+++ b/Assets/Documents/全局配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Projects\Unity\MagicSoup\Assets\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD5CF4F-9B5B-41D1-8FD3-040A84DF6BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C58F53-8734-4962-9079-47A1DFBA6A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="素材库" sheetId="1" r:id="rId1"/>
@@ -8325,7 +8325,7 @@
     <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="87" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>

--- a/Assets/Documents/全局配置表.xlsx
+++ b/Assets/Documents/全局配置表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Projects\Unity\MagicSoup\Assets\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\何睿豪\Documents\GitHub\MagicSoup\Assets\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C58F53-8734-4962-9079-47A1DFBA6A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C616AA3-08C2-4896-87EB-2B6814F12B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="素材库" sheetId="1" r:id="rId1"/>
@@ -26,16 +26,11 @@
     <sheet name="角色" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="576">
   <si>
     <t>ID</t>
   </si>
@@ -670,9 +665,6 @@
     <t>无-&gt;hp+3-&gt;无-&gt;无</t>
   </si>
   <si>
-    <t>战斗开始获得十格挡</t>
-  </si>
-  <si>
     <t>1-&gt;2-&gt;2-&gt;3-&gt;5</t>
   </si>
   <si>
@@ -682,34 +674,22 @@
     <t>无-&gt;hp+3-&gt;hp+3-&gt;hp+9</t>
   </si>
   <si>
-    <t>hp+29,增加意图：=2/5/8/11,打2*4</t>
-  </si>
-  <si>
     <t>海藻水+海藻气泡+海藻团块</t>
   </si>
   <si>
     <t>N1.4</t>
   </si>
   <si>
-    <t>hp+10</t>
-  </si>
-  <si>
     <t>任意水*3</t>
   </si>
   <si>
     <t>N1.5</t>
   </si>
   <si>
-    <t>回合结束所有伤害+1，hp+30,hp&lt;15时hp-10且获得15护盾</t>
-  </si>
-  <si>
     <t>特级混合精肉饼+硬面团+肉干</t>
   </si>
   <si>
     <t>N1.6</t>
-  </si>
-  <si>
-    <t>hp+15,每次行动执行意图执行两次</t>
   </si>
   <si>
     <t>任意肉饼+任意鸡蛋+任意水</t>
@@ -1708,6 +1688,106 @@
   </si>
   <si>
     <t>香料炖汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater0 Attack1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less10 Defence4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defence5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defence10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defence15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None Heal1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Heal5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Heal5all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清汤核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有清汤hp+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始获得十格挡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪腿核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp+29,增加意图：=2/5/8/11,打2*4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal1 Attack13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equal2/5/8/11,Attack2*4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp+29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束所有伤害+1，hp+30,hp&lt;15时hp-10且获得15护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp+15,每次行动执行意图执行两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芳香核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打击核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗港核心</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1755,7 +1835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1782,6 +1862,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1995,20 +2084,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="18" style="6" customWidth="1"/>
     <col min="3" max="3" width="9" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.4140625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="20.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="20.21875" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.33203125" style="2" customWidth="1"/>
     <col min="9" max="10" width="9" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2034,7 +2123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2054,7 +2143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2074,7 +2163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2094,7 +2183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2114,7 +2203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2134,7 +2223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2154,7 +2243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2174,7 +2263,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2194,7 +2283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2214,7 +2303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2234,7 +2323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -2254,7 +2343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -2274,7 +2363,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -2294,7 +2383,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -2314,7 +2403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -2334,7 +2423,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -2354,7 +2443,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -2374,7 +2463,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -2394,7 +2483,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -2408,7 +2497,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -2428,7 +2517,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -2448,7 +2537,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -2468,7 +2557,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -2485,7 +2574,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -2505,7 +2594,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -2525,7 +2614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -2545,7 +2634,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -2565,7 +2654,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -2582,7 +2671,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -2602,7 +2691,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2619,7 +2708,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2636,7 +2725,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -2653,7 +2742,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2670,7 +2759,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2687,7 +2776,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -2704,7 +2793,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2721,7 +2810,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2738,7 +2827,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -2749,7 +2838,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2760,7 +2849,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2771,7 +2860,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -2782,7 +2871,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2793,7 +2882,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2804,7 +2893,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -2815,7 +2904,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2826,7 +2915,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2837,7 +2926,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -2848,7 +2937,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2859,7 +2948,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2870,7 +2959,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -2881,7 +2970,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2892,7 +2981,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E53" s="5">
         <v>103</v>
       </c>
@@ -2900,7 +2989,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E54" s="5">
         <v>105</v>
       </c>
@@ -2908,7 +2997,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E55" s="5">
         <v>107</v>
       </c>
@@ -2916,7 +3005,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E56" s="5">
         <v>109</v>
       </c>
@@ -2924,7 +3013,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E57" s="5">
         <v>111</v>
       </c>
@@ -2932,7 +3021,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E58" s="5">
         <v>113</v>
       </c>
@@ -2940,7 +3029,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E59" s="5">
         <v>115</v>
       </c>
@@ -2948,7 +3037,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E60" s="5">
         <v>117</v>
       </c>
@@ -2956,7 +3045,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E61" s="5">
         <v>119</v>
       </c>
@@ -2964,7 +3053,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E62" s="5">
         <v>121</v>
       </c>
@@ -2981,12 +3070,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.25" customWidth="1"/>
+    <col min="2" max="2" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -2997,7 +3086,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>158</v>
       </c>
@@ -3008,7 +3097,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>160</v>
       </c>
@@ -3019,7 +3108,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>162</v>
       </c>
@@ -3030,7 +3119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>164</v>
       </c>
@@ -3041,7 +3130,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>167</v>
       </c>
@@ -3052,7 +3141,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -3063,132 +3152,132 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>196</v>
       </c>
@@ -3202,17 +3291,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H327"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="26.58203125" customWidth="1"/>
-    <col min="5" max="5" width="17.75" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="80" customWidth="1"/>
-    <col min="8" max="8" width="44.4140625" customWidth="1"/>
+    <col min="8" max="8" width="44.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -3238,7 +3327,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>203</v>
       </c>
@@ -3258,12 +3347,12 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>207</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
@@ -3277,45 +3366,45 @@
       <c r="F3" t="s">
         <v>210</v>
       </c>
-      <c r="G3" t="s">
-        <v>211</v>
+      <c r="G3" s="9" t="s">
+        <v>565</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>209</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" t="s">
         <v>213</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="H4" t="s">
         <v>214</v>
       </c>
-      <c r="G4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C5" t="s">
         <v>205</v>
@@ -3324,50 +3413,50 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G5" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>562</v>
       </c>
       <c r="H5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G6" t="s">
-        <v>221</v>
+        <v>213</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>571</v>
       </c>
       <c r="H6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C7" t="s">
         <v>205</v>
@@ -3376,2087 +3465,2087 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="H7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" t="s">
         <v>223</v>
       </c>
-      <c r="F7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G7" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E10" t="s">
         <v>224</v>
       </c>
-      <c r="H7" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" t="s">
         <v>226</v>
       </c>
-      <c r="H8" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E14" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>228</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E15" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>229</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E16" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>230</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E17" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>231</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E18" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>232</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E19" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>233</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E20" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>234</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E21" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>235</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E22" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>236</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E23" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>237</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E24" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>238</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E25" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>239</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E26" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>240</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E27" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>241</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E28" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>242</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E29" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>243</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E30" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>244</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E31" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>245</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E32" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>246</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E33" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>247</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E34" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>248</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E35" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>249</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E36" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>250</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E37" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>251</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E38" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>252</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E39" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>253</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E40" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>254</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E41" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>255</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E42" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>256</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E43" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>257</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E44" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>258</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E45" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>259</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E46" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>260</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E47" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>261</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E48" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>262</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E49" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>263</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E50" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>264</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E51" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>265</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E52" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>266</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E53" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>267</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E54" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>268</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E55" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>269</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E56" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>270</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E57" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>271</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E58" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>272</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E59" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>273</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E60" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>274</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E61" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>275</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E62" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>276</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E63" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>277</v>
-      </c>
-      <c r="E59" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="E64" t="s">
         <v>278</v>
       </c>
-      <c r="E60" t="s">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="E65" t="s">
         <v>279</v>
       </c>
-      <c r="E61" t="s">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="E66" t="s">
         <v>280</v>
       </c>
-      <c r="E62" t="s">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="E67" t="s">
         <v>281</v>
       </c>
-      <c r="E63" t="s">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="E68" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>283</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E69" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>284</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E70" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>285</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E71" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>286</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E72" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>287</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E73" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>288</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E74" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>289</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E75" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>290</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E76" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>291</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E77" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>292</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E78" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>293</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E79" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>294</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E80" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>295</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E81" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>296</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E82" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>297</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E83" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>298</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E84" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>299</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E85" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>300</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E86" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>301</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E87" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>302</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E88" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>303</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E89" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>304</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E90" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>305</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E91" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>306</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E92" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>307</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E93" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>308</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E94" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>309</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E95" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>310</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E96" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>311</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E97" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>312</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E98" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>313</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E99" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>314</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E100" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>315</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E101" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>316</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E102" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>317</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E103" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>318</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E104" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>319</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E105" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>320</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E106" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>321</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E107" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>322</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E108" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>323</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E109" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>324</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E110" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>325</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E111" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>326</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E112" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>327</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E113" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>328</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E114" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>329</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E115" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>330</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E116" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>331</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E117" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>332</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E118" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>333</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E119" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>334</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E120" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>335</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E121" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>336</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E122" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>337</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E123" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>338</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E124" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>339</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E125" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>340</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E126" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>341</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E127" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>342</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E128" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>343</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E129" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>344</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E130" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>345</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E131" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>346</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E132" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>347</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E133" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>348</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E134" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>349</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E135" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>350</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E136" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>351</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E137" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>352</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E138" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>353</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E139" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>354</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E140" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>355</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E141" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>356</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E142" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>357</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E143" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>358</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E144" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>359</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E145" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>360</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E146" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>361</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E147" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>362</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E148" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>363</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E149" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>364</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E150" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>365</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E151" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>366</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E152" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>367</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E153" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>368</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E154" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>369</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E155" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>370</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E156" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>371</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E157" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>372</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E158" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>373</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E159" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>374</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E160" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>375</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E161" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>376</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E162" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>377</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E163" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E164" t="s">
         <v>378</v>
       </c>
-      <c r="E159" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E165" t="s">
         <v>379</v>
       </c>
-      <c r="E160" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E166" t="s">
         <v>380</v>
       </c>
-      <c r="E161" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E167" t="s">
         <v>381</v>
       </c>
-      <c r="E162" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E168" t="s">
         <v>382</v>
       </c>
-      <c r="E163" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E164" t="s">
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E169" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E165" t="s">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E170" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E166" t="s">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E171" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E167" t="s">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E172" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E168" t="s">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E173" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E169" t="s">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E174" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E170" t="s">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E175" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E171" t="s">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E176" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E172" t="s">
+    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E177" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E173" t="s">
+    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E178" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E174" t="s">
+    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E179" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E175" t="s">
+    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E180" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E176" t="s">
+    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E181" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E177" t="s">
+    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E182" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E178" t="s">
+    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E183" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E179" t="s">
+    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E184" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E180" t="s">
+    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E185" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E181" t="s">
+    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E186" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E182" t="s">
+    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E187" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E183" t="s">
+    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E188" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E184" t="s">
+    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E189" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E185" t="s">
+    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E190" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E186" t="s">
+    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E191" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E187" t="s">
+    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E192" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E188" t="s">
+    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E193" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E189" t="s">
+    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E194" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E190" t="s">
+    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E195" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E191" t="s">
+    <row r="196" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E196" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E192" t="s">
+    <row r="197" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E197" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E193" t="s">
+    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E198" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E194" t="s">
+    <row r="199" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E199" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E195" t="s">
+    <row r="200" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E200" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="196" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E196" t="s">
+    <row r="201" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E201" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="197" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E197" t="s">
+    <row r="202" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E202" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E198" t="s">
+    <row r="203" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E203" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="199" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E199" t="s">
+    <row r="204" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E204" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="200" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E200" t="s">
+    <row r="205" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E205" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="201" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E201" t="s">
+    <row r="206" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E206" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="202" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E202" t="s">
+    <row r="207" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E207" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="203" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E203" t="s">
+    <row r="208" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E208" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="204" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E204" t="s">
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E209" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="205" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E205" t="s">
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E210" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="206" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E206" t="s">
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E211" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="207" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E207" t="s">
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E212" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="208" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E208" t="s">
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E213" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E209" t="s">
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E214" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E210" t="s">
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E215" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E211" t="s">
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E216" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E212" t="s">
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E213" t="s">
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E218" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E214" t="s">
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E219" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E215" t="s">
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E220" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E216" t="s">
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E221" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E217" t="s">
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E222" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="218" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E218" t="s">
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E223" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E219" t="s">
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E224" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E220" t="s">
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E225" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E221" t="s">
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E226" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E222" t="s">
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E227" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E223" t="s">
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E228" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E224" t="s">
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E229" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E225" t="s">
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E230" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E226" t="s">
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E231" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E227" t="s">
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E232" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E228" t="s">
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E233" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E229" t="s">
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E234" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E230" t="s">
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E235" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E231" t="s">
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E236" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E232" t="s">
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E237" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="233" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E233" t="s">
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E238" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E234" t="s">
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E239" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E235" t="s">
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E240" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E236" t="s">
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E241" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E237" t="s">
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E242" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E238" t="s">
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E243" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E239" t="s">
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E244" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E240" t="s">
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E245" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E241" t="s">
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E246" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E242" t="s">
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E247" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E243" t="s">
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E248" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E244" t="s">
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E249" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E245" t="s">
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E250" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E246" t="s">
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E251" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E247" t="s">
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E252" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="248" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E248" t="s">
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E253" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="249" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E249" t="s">
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E254" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="250" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E250" t="s">
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E255" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="251" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E251" t="s">
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E256" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="252" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E252" t="s">
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E257" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="253" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E253" t="s">
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E258" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="254" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E254" t="s">
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E259" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="255" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E255" t="s">
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E260" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="256" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E256" t="s">
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E261" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="257" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E257" t="s">
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E262" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="258" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E258" t="s">
+    <row r="263" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E263" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="259" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E259" t="s">
+    <row r="264" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E264" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="260" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E260" t="s">
+    <row r="265" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E265" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="261" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E261" t="s">
+    <row r="266" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E266" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="262" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E262" t="s">
+    <row r="267" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E267" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="263" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E263" t="s">
+    <row r="268" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E268" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="264" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E264" t="s">
+    <row r="269" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E269" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="265" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E265" t="s">
+    <row r="270" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E270" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="266" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E266" t="s">
+    <row r="271" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E271" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="267" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E267" t="s">
+    <row r="272" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E272" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="268" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E268" t="s">
+    <row r="273" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E273" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="269" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E269" t="s">
+    <row r="274" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E274" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="270" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E270" t="s">
+    <row r="275" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E275" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="271" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E271" t="s">
+    <row r="276" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E276" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="272" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E272" t="s">
+    <row r="277" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E277" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="273" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E273" t="s">
+    <row r="278" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E278" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="274" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E274" t="s">
+    <row r="279" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E279" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="275" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E275" t="s">
+    <row r="280" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E280" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="276" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E276" t="s">
+    <row r="281" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E281" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="277" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E277" t="s">
+    <row r="282" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E282" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="278" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E278" t="s">
+    <row r="283" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E283" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="279" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E279" t="s">
+    <row r="284" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E284" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="280" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E280" t="s">
+    <row r="285" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E285" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="281" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E281" t="s">
+    <row r="286" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E286" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="282" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E282" t="s">
+    <row r="287" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E287" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="283" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E283" t="s">
+    <row r="288" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E288" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="284" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E284" t="s">
+    <row r="289" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E289" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="285" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E285" t="s">
+    <row r="290" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E290" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="286" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E286" t="s">
+    <row r="291" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E291" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="287" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E287" t="s">
+    <row r="292" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E292" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="288" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E288" t="s">
+    <row r="293" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E293" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="289" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E289" t="s">
+    <row r="294" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E294" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="290" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E290" t="s">
+    <row r="295" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E295" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="291" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E291" t="s">
+    <row r="296" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E296" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="292" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E292" t="s">
+    <row r="297" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E297" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="293" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E293" t="s">
+    <row r="298" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E298" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="294" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E294" t="s">
+    <row r="299" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E299" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="295" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E295" t="s">
+    <row r="300" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E300" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="296" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E296" t="s">
+    <row r="301" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E301" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="297" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E297" t="s">
+    <row r="302" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E302" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="298" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E298" t="s">
+    <row r="303" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E303" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="299" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E299" t="s">
+    <row r="304" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E304" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="300" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E300" t="s">
+    <row r="305" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E305" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="301" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E301" t="s">
+    <row r="306" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E306" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="302" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E302" t="s">
+    <row r="307" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E307" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="303" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E303" t="s">
+    <row r="308" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E308" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="304" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E304" t="s">
+    <row r="309" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E309" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="305" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E305" t="s">
+    <row r="310" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E310" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="306" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E306" t="s">
+    <row r="311" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E311" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="307" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E307" t="s">
+    <row r="312" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E312" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="308" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E308" t="s">
+    <row r="313" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E313" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="309" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E309" t="s">
+    <row r="314" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E314" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="310" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E310" t="s">
+    <row r="315" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E315" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="311" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E311" t="s">
+    <row r="316" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E316" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="312" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E312" t="s">
+    <row r="317" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E317" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="313" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E313" t="s">
+    <row r="318" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E318" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="314" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E314" t="s">
+    <row r="319" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E319" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="315" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E315" t="s">
+    <row r="320" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E320" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="316" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E316" t="s">
+    <row r="321" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E321" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="317" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E317" t="s">
+    <row r="322" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E322" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="318" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E318" t="s">
+    <row r="323" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E323" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="319" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E319" t="s">
+    <row r="324" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E324" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="320" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E320" t="s">
+    <row r="325" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E325" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="321" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E321" t="s">
+    <row r="326" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E326" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="322" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E322" t="s">
+    <row r="327" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E327" t="s">
         <v>541</v>
-      </c>
-    </row>
-    <row r="323" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E323" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="324" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E324" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="325" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E325" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="326" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E326" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="327" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E327" t="s">
-        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -5469,23 +5558,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L256"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.9140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="119.58203125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="119.5546875" style="7" customWidth="1"/>
     <col min="6" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20.77734375" style="2" customWidth="1"/>
     <col min="10" max="10" width="9" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.21875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" style="2" customWidth="1"/>
     <col min="13" max="14" width="9" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="92" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="91.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5499,7 +5588,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5510,7 +5599,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -5521,7 +5610,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -5532,7 +5621,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5543,7 +5632,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5560,7 +5649,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -5577,7 +5666,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -5588,7 +5677,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -5599,7 +5688,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -5610,7 +5699,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -5621,7 +5710,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -5638,7 +5727,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -5655,7 +5744,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -5666,7 +5755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -5677,7 +5766,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -5688,7 +5777,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -5699,7 +5788,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="8.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -5716,7 +5805,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="8.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -5733,7 +5822,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -5747,7 +5836,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -5761,7 +5850,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -5775,7 +5864,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -5789,7 +5878,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -5803,7 +5892,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -5817,7 +5906,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -5825,7 +5914,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -5833,7 +5922,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -5844,7 +5933,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -5855,7 +5944,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -5869,7 +5958,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -5883,7 +5972,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -5894,7 +5983,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -5905,7 +5994,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -5913,7 +6002,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -5921,7 +6010,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -5929,7 +6018,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -5937,7 +6026,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -5945,7 +6034,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -5953,7 +6042,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -5964,7 +6053,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -5975,7 +6064,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5983,7 +6072,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -5991,7 +6080,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -6002,7 +6091,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -6013,7 +6102,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -6024,7 +6113,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -6035,7 +6124,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -6046,7 +6135,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -6057,7 +6146,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -6068,7 +6157,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -6079,19 +6168,19 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -6106,7 +6195,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -6121,13 +6210,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5" t="s">
-        <v>100</v>
+      <c r="B56" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>568</v>
       </c>
       <c r="D56" t="s">
         <v>101</v>
@@ -6136,11 +6227,13 @@
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="5"/>
+      <c r="B57" s="11" t="s">
+        <v>569</v>
+      </c>
       <c r="C57" s="5" t="s">
         <v>100</v>
       </c>
@@ -6151,18 +6244,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C58" s="11" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -6173,7 +6266,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -6181,7 +6274,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -6189,7 +6282,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -6197,7 +6290,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -6205,21 +6298,21 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>105</v>
+      <c r="C64" s="10" t="s">
+        <v>551</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -6229,11 +6322,11 @@
       <c r="C65" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D65" s="10" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -6241,7 +6334,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -6249,7 +6342,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -6257,7 +6350,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -6265,7 +6358,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -6273,7 +6366,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -6281,7 +6374,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -6289,7 +6382,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -6297,7 +6390,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -6305,7 +6398,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -6313,907 +6406,931 @@
         <v>113</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B76" s="10" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B77" s="10" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B78" s="10" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B79" s="10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B80" s="10" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B81" s="10" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B82" s="10" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B83" s="10" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>212</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>239</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>245</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>252</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>254</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>255</v>
       </c>
@@ -7227,12 +7344,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.9140625" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7243,7 +7360,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7251,10 +7368,10 @@
         <v>115</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7262,10 +7379,10 @@
         <v>116</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7273,10 +7390,10 @@
         <v>117</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7284,10 +7401,10 @@
         <v>118</v>
       </c>
       <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7295,10 +7412,10 @@
         <v>119</v>
       </c>
       <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7306,10 +7423,10 @@
         <v>120</v>
       </c>
       <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7317,10 +7434,10 @@
         <v>121</v>
       </c>
       <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7328,7 +7445,7 @@
         <v>122</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -7340,15 +7457,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="45.4140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.44140625" style="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7356,7 +7473,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -7364,7 +7481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -7372,7 +7489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -7380,7 +7497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -7388,7 +7505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -7396,7 +7513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -7404,7 +7521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -7412,7 +7529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -7420,7 +7537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -7428,7 +7545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -7436,7 +7553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -7444,7 +7561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -7452,7 +7569,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -7460,7 +7577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -7468,7 +7585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -7476,7 +7593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -7484,7 +7601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -7492,7 +7609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -7500,7 +7617,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -7508,7 +7625,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -7516,7 +7633,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -7524,7 +7641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -7532,7 +7649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -7540,7 +7657,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -7548,7 +7665,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26"/>
     </row>
   </sheetData>
@@ -7560,20 +7677,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="64.58203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="26.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.9140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" style="1" customWidth="1"/>
     <col min="8" max="9" width="9" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="64.349999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -7596,7 +7713,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="63.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="63.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -7604,7 +7721,7 @@
         <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D2">
         <v>45</v>
@@ -7616,7 +7733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -7624,7 +7741,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="D3">
         <v>55</v>
@@ -7636,7 +7753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -7656,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -7676,7 +7793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -7696,7 +7813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -7716,7 +7833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -7736,7 +7853,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -7756,7 +7873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -7764,7 +7881,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D10" s="1">
         <v>71</v>
@@ -7776,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -7796,7 +7913,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>564</v>
+      </c>
       <c r="D12" s="1">
         <v>75</v>
       </c>
@@ -7804,7 +7930,16 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>565</v>
+      </c>
       <c r="D13" s="1">
         <v>77</v>
       </c>
@@ -7812,7 +7947,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>570</v>
+      </c>
       <c r="D14" s="1">
         <v>79</v>
       </c>
@@ -7820,7 +7964,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>571</v>
+      </c>
       <c r="D15" s="1">
         <v>81</v>
       </c>
@@ -7828,7 +7981,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>572</v>
+      </c>
       <c r="D16" s="1">
         <v>83</v>
       </c>
@@ -7836,7 +7998,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D17" s="1">
         <v>85</v>
       </c>
@@ -7844,7 +8006,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <v>87</v>
       </c>
@@ -7852,7 +8014,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="1">
         <v>89</v>
       </c>
@@ -7860,7 +8022,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D20" s="1">
         <v>91</v>
       </c>
@@ -7868,7 +8030,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D21" s="1">
         <v>93</v>
       </c>
@@ -7876,7 +8038,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D22" s="1">
         <v>95</v>
       </c>
@@ -7884,7 +8046,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D23" s="1">
         <v>97</v>
       </c>
@@ -7892,7 +8054,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D24" s="1">
         <v>99</v>
       </c>
@@ -7900,7 +8062,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D25" s="1">
         <v>101</v>
       </c>
@@ -7908,7 +8070,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D26" s="1">
         <v>103</v>
       </c>
@@ -7916,7 +8078,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D27" s="1">
         <v>105</v>
       </c>
@@ -7924,7 +8086,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D28" s="1">
         <v>107</v>
       </c>
@@ -7932,7 +8094,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D29" s="1">
         <v>109</v>
       </c>
@@ -7940,7 +8102,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D30" s="1">
         <v>111</v>
       </c>
@@ -7948,7 +8110,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D31" s="1">
         <v>113</v>
       </c>
@@ -7956,7 +8118,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D32" s="1">
         <v>115</v>
       </c>
@@ -7964,7 +8126,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D33" s="1">
         <v>117</v>
       </c>
@@ -7972,7 +8134,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D34" s="1">
         <v>119</v>
       </c>
@@ -7980,7 +8142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D35" s="1">
         <v>121</v>
       </c>
@@ -7988,7 +8150,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D36" s="1">
         <v>123</v>
       </c>
@@ -7996,7 +8158,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D37" s="1">
         <v>125</v>
       </c>
@@ -8004,7 +8166,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D38" s="1">
         <v>127</v>
       </c>
@@ -8012,7 +8174,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D39" s="1">
         <v>129</v>
       </c>
@@ -8020,7 +8182,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D40" s="1">
         <v>131</v>
       </c>
@@ -8028,7 +8190,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D41" s="1">
         <v>133</v>
       </c>
@@ -8036,7 +8198,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D42" s="1">
         <v>135</v>
       </c>
@@ -8044,7 +8206,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="43" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D43" s="1">
         <v>137</v>
       </c>
@@ -8052,7 +8214,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D44" s="1">
         <v>139</v>
       </c>
@@ -8060,7 +8222,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D45" s="1">
         <v>141</v>
       </c>
@@ -8068,7 +8230,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D46" s="1">
         <v>143</v>
       </c>
@@ -8076,7 +8238,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D47" s="1">
         <v>145</v>
       </c>
@@ -8084,7 +8246,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D48" s="1">
         <v>147</v>
       </c>
@@ -8092,7 +8254,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D49" s="1">
         <v>149</v>
       </c>
@@ -8100,7 +8262,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D50" s="1">
         <v>151</v>
       </c>
@@ -8108,7 +8270,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="51" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D51" s="1">
         <v>153</v>
       </c>
@@ -8116,7 +8278,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="52" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D52" s="1">
         <v>155</v>
       </c>
@@ -8124,7 +8286,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="53" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D53" s="1">
         <v>157</v>
       </c>
@@ -8132,7 +8294,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D54" s="1">
         <v>159</v>
       </c>
@@ -8140,7 +8302,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D55" s="1">
         <v>161</v>
       </c>
@@ -8148,7 +8310,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="56" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D56" s="1">
         <v>163</v>
       </c>
@@ -8156,7 +8318,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D57" s="1">
         <v>165</v>
       </c>
@@ -8164,7 +8326,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D58" s="1">
         <v>167</v>
       </c>
@@ -8172,7 +8334,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D59" s="1">
         <v>169</v>
       </c>
@@ -8180,7 +8342,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="60" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D60" s="1">
         <v>171</v>
       </c>
@@ -8188,7 +8350,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="61" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D61" s="1">
         <v>173</v>
       </c>
@@ -8196,7 +8358,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="62" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D62" s="1">
         <v>175</v>
       </c>
@@ -8204,7 +8366,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D63" s="1">
         <v>177</v>
       </c>
@@ -8212,7 +8374,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D64" s="1">
         <v>179</v>
       </c>
@@ -8220,7 +8382,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D65" s="1">
         <v>181</v>
       </c>
@@ -8237,12 +8399,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.4140625" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8250,7 +8412,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8258,7 +8420,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8266,7 +8428,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8274,7 +8436,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8282,7 +8444,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8290,7 +8452,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8298,7 +8460,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8315,17 +8477,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="9" style="3" customWidth="1"/>
     <col min="6" max="6" width="15" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.4140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" style="3" customWidth="1"/>
     <col min="9" max="10" width="9" style="3" customWidth="1"/>
     <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8351,7 +8513,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -8374,12 +8536,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8402,28 +8564,37 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="9" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F3" s="9" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>151</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -8435,12 +8606,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>124</v>
       </c>
@@ -8463,20 +8634,26 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="9" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>154</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>574</v>
       </c>
     </row>
   </sheetData>
